--- a/research/traditional_assets/database/data/belgium/belgium_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_drugs_pharmaceutical.xlsx
@@ -1519,7 +1519,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1656,22 +1656,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09115863951961459</v>
+        <v>0.09096449292081554</v>
       </c>
       <c r="C2">
-        <v>40024.69803957342</v>
+        <v>39784.71306706555</v>
       </c>
       <c r="D2">
-        <v>39566.09803957342</v>
+        <v>39736.17906706555</v>
       </c>
       <c r="E2">
-        <v>-3255.1</v>
+        <v>-2845.034</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>410.066</v>
       </c>
       <c r="G2">
         <v>458.6</v>
@@ -1692,28 +1692,28 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>20.6263198</v>
       </c>
       <c r="N2">
-        <v>552.0122448979592</v>
+        <v>531.3859250979592</v>
       </c>
       <c r="O2">
-        <v>138.0030612244898</v>
+        <v>132.8464812744898</v>
       </c>
       <c r="P2">
-        <v>414.0091836734695</v>
+        <v>398.5394438234694</v>
       </c>
       <c r="Q2">
-        <v>1157.609183673469</v>
+        <v>1142.139443823469</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09115863951961459</v>
+        <v>0.09150226557658137</v>
       </c>
       <c r="T2">
-        <v>0.8841243102286289</v>
+        <v>0.8908222216697549</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>26.76251751405306</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1738,22 +1738,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09096449292081554</v>
+        <v>0.09077034632201653</v>
       </c>
       <c r="C3">
-        <v>39784.71306706555</v>
+        <v>39546.19664686859</v>
       </c>
       <c r="D3">
-        <v>39736.17906706555</v>
+        <v>39907.72864686859</v>
       </c>
       <c r="E3">
-        <v>-2845.034</v>
+        <v>-2434.968</v>
       </c>
       <c r="F3">
-        <v>410.066</v>
+        <v>820.1319999999999</v>
       </c>
       <c r="G3">
         <v>458.6</v>
@@ -1774,28 +1774,28 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M3">
-        <v>20.6263198</v>
+        <v>41.25263959999999</v>
       </c>
       <c r="N3">
-        <v>531.3859250979592</v>
+        <v>510.7596052979592</v>
       </c>
       <c r="O3">
-        <v>132.8464812744898</v>
+        <v>127.6899013244898</v>
       </c>
       <c r="P3">
-        <v>398.5394438234694</v>
+        <v>383.0697039734694</v>
       </c>
       <c r="Q3">
-        <v>1142.139443823469</v>
+        <v>1126.669703973469</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09150226557658137</v>
+        <v>0.09185290441022094</v>
       </c>
       <c r="T3">
-        <v>0.8908222216697549</v>
+        <v>0.897656825181108</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>26.76251751405306</v>
+        <v>13.38125875702653</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1820,22 +1820,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09077034632201653</v>
+        <v>0.09057619972321747</v>
       </c>
       <c r="C4">
-        <v>39546.19664686859</v>
+        <v>39309.1678816156</v>
       </c>
       <c r="D4">
-        <v>39907.72864686859</v>
+        <v>40080.7658816156</v>
       </c>
       <c r="E4">
-        <v>-2434.968</v>
+        <v>-2024.902</v>
       </c>
       <c r="F4">
-        <v>820.1319999999999</v>
+        <v>1230.198</v>
       </c>
       <c r="G4">
         <v>458.6</v>
@@ -1856,28 +1856,28 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M4">
-        <v>41.25263959999999</v>
+        <v>61.87895939999999</v>
       </c>
       <c r="N4">
-        <v>510.7596052979592</v>
+        <v>490.1332854979593</v>
       </c>
       <c r="O4">
-        <v>127.6899013244898</v>
+        <v>122.5333213744898</v>
       </c>
       <c r="P4">
-        <v>383.0697039734694</v>
+        <v>367.5999641234695</v>
       </c>
       <c r="Q4">
-        <v>1126.669703973469</v>
+        <v>1111.199964123469</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09185290441022094</v>
+        <v>0.09221077291053348</v>
       </c>
       <c r="T4">
-        <v>0.897656825181108</v>
+        <v>0.9046323483524888</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1894,7 +1894,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>13.38125875702653</v>
+        <v>8.92083917135102</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1902,22 +1902,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09057619972321747</v>
+        <v>0.09047805312441842</v>
       </c>
       <c r="C5">
-        <v>39309.1678816156</v>
+        <v>38987.14938085614</v>
       </c>
       <c r="D5">
-        <v>40080.7658816156</v>
+        <v>40168.81338085615</v>
       </c>
       <c r="E5">
-        <v>-2024.902</v>
+        <v>-1614.836</v>
       </c>
       <c r="F5">
-        <v>1230.198</v>
+        <v>1640.264</v>
       </c>
       <c r="G5">
         <v>458.6</v>
@@ -1938,45 +1938,45 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M5">
-        <v>61.87895939999999</v>
+        <v>87.75412399999999</v>
       </c>
       <c r="N5">
-        <v>490.1332854979593</v>
+        <v>464.2581208979593</v>
       </c>
       <c r="O5">
-        <v>122.5333213744898</v>
+        <v>116.0645302244898</v>
       </c>
       <c r="P5">
-        <v>367.5999641234695</v>
+        <v>348.1935906734694</v>
       </c>
       <c r="Q5">
-        <v>1111.199964123469</v>
+        <v>1091.793590673469</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09221077291053348</v>
+        <v>0.09257609700460254</v>
       </c>
       <c r="T5">
-        <v>0.9046323483524888</v>
+        <v>0.9117531949232736</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.03772499999999999</v>
+        <v>0.040125</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>8.92083917135102</v>
+        <v>6.290442200733032</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1984,22 +1984,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09047805312441842</v>
+        <v>0.0903379065256194</v>
       </c>
       <c r="C6">
-        <v>38987.14938085614</v>
+        <v>38703.48183584148</v>
       </c>
       <c r="D6">
-        <v>40168.81338085615</v>
+        <v>40295.21183584148</v>
       </c>
       <c r="E6">
-        <v>-1614.836</v>
+        <v>-1204.77</v>
       </c>
       <c r="F6">
-        <v>1640.264</v>
+        <v>2050.33</v>
       </c>
       <c r="G6">
         <v>458.6</v>
@@ -2020,45 +2020,45 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M6">
-        <v>87.75412399999999</v>
+        <v>111.332919</v>
       </c>
       <c r="N6">
-        <v>464.2581208979593</v>
+        <v>440.6793258979592</v>
       </c>
       <c r="O6">
-        <v>116.0645302244898</v>
+        <v>110.1698314744898</v>
       </c>
       <c r="P6">
-        <v>348.1935906734694</v>
+        <v>330.5094944234694</v>
       </c>
       <c r="Q6">
-        <v>1091.793590673469</v>
+        <v>1074.109494423469</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09257609700460254</v>
+        <v>0.09294911213223095</v>
       </c>
       <c r="T6">
-        <v>0.9117531949232736</v>
+        <v>0.9190239540534433</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>6.290442200733032</v>
+        <v>4.958212268717748</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2066,22 +2066,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0903379065256194</v>
+        <v>0.09021875992682037</v>
       </c>
       <c r="C7">
-        <v>38703.48183584148</v>
+        <v>38401.50164116421</v>
       </c>
       <c r="D7">
-        <v>40295.21183584148</v>
+        <v>40403.29764116421</v>
       </c>
       <c r="E7">
-        <v>-1204.77</v>
+        <v>-794.7039999999997</v>
       </c>
       <c r="F7">
-        <v>2050.33</v>
+        <v>2460.396</v>
       </c>
       <c r="G7">
         <v>458.6</v>
@@ -2102,45 +2102,45 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M7">
-        <v>111.332919</v>
+        <v>136.0598988</v>
       </c>
       <c r="N7">
-        <v>440.6793258979592</v>
+        <v>415.9523460979592</v>
       </c>
       <c r="O7">
-        <v>110.1698314744898</v>
+        <v>103.9880865244898</v>
       </c>
       <c r="P7">
-        <v>330.5094944234694</v>
+        <v>311.9642595734694</v>
       </c>
       <c r="Q7">
-        <v>1074.109494423469</v>
+        <v>1055.564259573469</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09294911213223095</v>
+        <v>0.09333006375193656</v>
       </c>
       <c r="T7">
-        <v>0.9190239540534433</v>
+        <v>0.9264494101863824</v>
       </c>
       <c r="U7">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>4.958212268717748</v>
+        <v>4.057126675578266</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2148,22 +2148,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09021875992682037</v>
+        <v>0.09006211332802133</v>
       </c>
       <c r="C8">
-        <v>38401.50164116421</v>
+        <v>38134.42563147149</v>
       </c>
       <c r="D8">
-        <v>40403.29764116421</v>
+        <v>40546.28763147149</v>
       </c>
       <c r="E8">
-        <v>-794.7040000000002</v>
+        <v>-384.6380000000004</v>
       </c>
       <c r="F8">
-        <v>2460.396</v>
+        <v>2870.462</v>
       </c>
       <c r="G8">
         <v>458.6</v>
@@ -2184,28 +2184,28 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M8">
-        <v>136.0598988</v>
+        <v>158.7365486</v>
       </c>
       <c r="N8">
-        <v>415.9523460979593</v>
+        <v>393.2756962979593</v>
       </c>
       <c r="O8">
-        <v>103.9880865244898</v>
+        <v>98.31892407448981</v>
       </c>
       <c r="P8">
-        <v>311.9642595734695</v>
+        <v>294.9567722234694</v>
       </c>
       <c r="Q8">
-        <v>1055.564259573469</v>
+        <v>1038.55677222347</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09333006375193656</v>
+        <v>0.09371920787959283</v>
       </c>
       <c r="T8">
-        <v>0.9264494101863824</v>
+        <v>0.9340345535479869</v>
       </c>
       <c r="U8">
         <v>0.0553</v>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>4.057126675578266</v>
+        <v>3.477537150495656</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2230,22 +2230,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09006211332802132</v>
+        <v>0.08990546672922231</v>
       </c>
       <c r="C9">
-        <v>38134.4256314715</v>
+        <v>37868.3653188025</v>
       </c>
       <c r="D9">
-        <v>40546.2876314715</v>
+        <v>40690.2933188025</v>
       </c>
       <c r="E9">
-        <v>-384.6379999999999</v>
+        <v>25.42799999999988</v>
       </c>
       <c r="F9">
-        <v>2870.462</v>
+        <v>3280.528</v>
       </c>
       <c r="G9">
         <v>458.6</v>
@@ -2266,28 +2266,28 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M9">
-        <v>158.7365486</v>
+        <v>181.4131984</v>
       </c>
       <c r="N9">
-        <v>393.2756962979593</v>
+        <v>370.5990464979593</v>
       </c>
       <c r="O9">
-        <v>98.31892407448981</v>
+        <v>92.64976162448981</v>
       </c>
       <c r="P9">
-        <v>294.9567722234694</v>
+        <v>277.9492848734694</v>
       </c>
       <c r="Q9">
-        <v>1038.55677222347</v>
+        <v>1021.549284873469</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09371920787959283</v>
+        <v>0.09411681166219815</v>
       </c>
       <c r="T9">
-        <v>0.9340345535479869</v>
+        <v>0.9417845913304961</v>
       </c>
       <c r="U9">
         <v>0.0553</v>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>3.477537150495656</v>
+        <v>3.042845006683699</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2312,22 +2312,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08990546672922231</v>
+        <v>0.08991757013042327</v>
       </c>
       <c r="C10">
-        <v>37868.3653188025</v>
+        <v>37447.13617125004</v>
       </c>
       <c r="D10">
-        <v>40690.2933188025</v>
+        <v>40679.13017125004</v>
       </c>
       <c r="E10">
-        <v>25.42799999999988</v>
+        <v>435.4939999999997</v>
       </c>
       <c r="F10">
-        <v>3280.528</v>
+        <v>3690.594</v>
       </c>
       <c r="G10">
         <v>458.6</v>
@@ -2348,45 +2348,45 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M10">
-        <v>181.4131984</v>
+        <v>213.3163332</v>
       </c>
       <c r="N10">
-        <v>370.5990464979593</v>
+        <v>338.6959116979592</v>
       </c>
       <c r="O10">
-        <v>92.64976162448981</v>
+        <v>84.6739779244898</v>
       </c>
       <c r="P10">
-        <v>277.9492848734694</v>
+        <v>254.0219337734694</v>
       </c>
       <c r="Q10">
-        <v>1021.549284873469</v>
+        <v>997.6219337734694</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09411681166219815</v>
+        <v>0.09452315398947611</v>
       </c>
       <c r="T10">
-        <v>0.9417845913304961</v>
+        <v>0.9497049596137195</v>
       </c>
       <c r="U10">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.042845006683699</v>
+        <v>2.587763611989367</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2394,22 +2394,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08991757013042327</v>
+        <v>0.09025217353162422</v>
       </c>
       <c r="C11">
-        <v>37447.13617125004</v>
+        <v>36730.86747671783</v>
       </c>
       <c r="D11">
-        <v>40679.13017125004</v>
+        <v>40372.92747671783</v>
       </c>
       <c r="E11">
-        <v>435.4939999999997</v>
+        <v>845.5599999999999</v>
       </c>
       <c r="F11">
-        <v>3690.594</v>
+        <v>4100.66</v>
       </c>
       <c r="G11">
         <v>458.6</v>
@@ -2430,45 +2430,45 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M11">
-        <v>213.3163332</v>
+        <v>262.852306</v>
       </c>
       <c r="N11">
-        <v>338.6959116979592</v>
+        <v>289.1599388979593</v>
       </c>
       <c r="O11">
-        <v>84.6739779244898</v>
+        <v>72.28998472448981</v>
       </c>
       <c r="P11">
-        <v>254.0219337734694</v>
+        <v>216.8699541734694</v>
       </c>
       <c r="Q11">
-        <v>997.6219337734694</v>
+        <v>960.4699541734694</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09452315398947611</v>
+        <v>0.09493852614624913</v>
       </c>
       <c r="T11">
-        <v>0.9497049596137195</v>
+        <v>0.9578013360810146</v>
       </c>
       <c r="U11">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04335</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.587763611989367</v>
+        <v>2.100085227701823</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2476,22 +2476,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09025217353162422</v>
+        <v>0.09112677693282518</v>
       </c>
       <c r="C12">
-        <v>36730.86747671783</v>
+        <v>35541.78514074698</v>
       </c>
       <c r="D12">
-        <v>40372.92747671783</v>
+        <v>39593.91114074698</v>
       </c>
       <c r="E12">
-        <v>845.5599999999999</v>
+        <v>1255.626</v>
       </c>
       <c r="F12">
-        <v>4100.66</v>
+        <v>4510.726</v>
       </c>
       <c r="G12">
         <v>458.6</v>
@@ -2512,45 +2512,45 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M12">
-        <v>262.852306</v>
+        <v>341.9130308</v>
       </c>
       <c r="N12">
-        <v>289.1599388979593</v>
+        <v>210.0992140979592</v>
       </c>
       <c r="O12">
-        <v>72.28998472448981</v>
+        <v>52.52480352448981</v>
       </c>
       <c r="P12">
-        <v>216.8699541734694</v>
+        <v>157.5744105734694</v>
       </c>
       <c r="Q12">
-        <v>960.4699541734694</v>
+        <v>901.1744105734695</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09493852614624913</v>
+        <v>0.09536323250879235</v>
       </c>
       <c r="T12">
-        <v>0.9578013360810146</v>
+        <v>0.9660796535925187</v>
       </c>
       <c r="U12">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04807500000000001</v>
+        <v>0.05685</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y12">
-        <v>2.100085227701823</v>
+        <v>1.614481447537621</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2558,22 +2558,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09112677693282518</v>
+        <v>0.09524215887301432</v>
       </c>
       <c r="C13">
-        <v>35541.78514074698</v>
+        <v>31836.06881794081</v>
       </c>
       <c r="D13">
-        <v>39593.91114074698</v>
+        <v>36298.26081794081</v>
       </c>
       <c r="E13">
-        <v>1255.626</v>
+        <v>1665.692</v>
       </c>
       <c r="F13">
-        <v>4510.726</v>
+        <v>4920.791999999999</v>
       </c>
       <c r="G13">
         <v>458.6</v>
@@ -2594,45 +2594,45 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M13">
-        <v>341.9130308</v>
+        <v>583.6059312</v>
       </c>
       <c r="N13">
-        <v>210.0992140979592</v>
+        <v>-31.59368630204074</v>
       </c>
       <c r="O13">
-        <v>52.52480352448981</v>
+        <v>-7.898421575510184</v>
       </c>
       <c r="P13">
-        <v>157.5744105734694</v>
+        <v>-23.69526472653055</v>
       </c>
       <c r="Q13">
-        <v>901.1744105734695</v>
+        <v>719.9047352734694</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09536323250879235</v>
+        <v>0.09588130164818918</v>
       </c>
       <c r="T13">
-        <v>0.9660796535925187</v>
+        <v>0.9761777854009451</v>
       </c>
       <c r="U13">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V13">
-        <v>0.25</v>
+        <v>0.2364661732287923</v>
       </c>
       <c r="W13">
-        <v>0.05685</v>
+        <v>0.09055511185506525</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y13">
-        <v>1.614481447537621</v>
+        <v>0.9458646929151691</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2640,22 +2640,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09524215887301432</v>
+        <v>0.09597015887301431</v>
       </c>
       <c r="C14">
-        <v>31836.06881794081</v>
+        <v>30899.29262867581</v>
       </c>
       <c r="D14">
-        <v>36298.26081794081</v>
+        <v>35771.55062867581</v>
       </c>
       <c r="E14">
-        <v>1665.692</v>
+        <v>2075.758</v>
       </c>
       <c r="F14">
-        <v>4920.791999999999</v>
+        <v>5330.858</v>
       </c>
       <c r="G14">
         <v>458.6</v>
@@ -2676,37 +2676,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M14">
-        <v>583.6059312</v>
+        <v>632.2397588000001</v>
       </c>
       <c r="N14">
-        <v>-31.59368630204074</v>
+        <v>-80.22751390204087</v>
       </c>
       <c r="O14">
-        <v>-7.898421575510184</v>
+        <v>-20.05687847551022</v>
       </c>
       <c r="P14">
-        <v>-23.69526472653055</v>
+        <v>-60.17063542653065</v>
       </c>
       <c r="Q14">
-        <v>719.9047352734694</v>
+        <v>683.4293645734693</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09588130164818918</v>
+        <v>0.09645694879357067</v>
       </c>
       <c r="T14">
-        <v>0.9761777854009451</v>
+        <v>0.9873982197158987</v>
       </c>
       <c r="U14">
         <v>0.1186</v>
       </c>
       <c r="V14">
-        <v>0.2364661732287923</v>
+        <v>0.2182764675958082</v>
       </c>
       <c r="W14">
-        <v>0.09055511185506525</v>
+        <v>0.09271241094313716</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.9458646929151691</v>
+        <v>0.8731058703832327</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2722,22 +2722,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09597015887301431</v>
+        <v>0.09669815887301432</v>
       </c>
       <c r="C15">
-        <v>30899.29262867581</v>
+        <v>29977.583586289</v>
       </c>
       <c r="D15">
-        <v>35771.55062867581</v>
+        <v>35259.907586289</v>
       </c>
       <c r="E15">
-        <v>2075.758</v>
+        <v>2485.824</v>
       </c>
       <c r="F15">
-        <v>5330.858</v>
+        <v>5740.924</v>
       </c>
       <c r="G15">
         <v>458.6</v>
@@ -2758,37 +2758,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M15">
-        <v>632.2397588000001</v>
+        <v>680.8735864</v>
       </c>
       <c r="N15">
-        <v>-80.22751390204087</v>
+        <v>-128.8613415020408</v>
       </c>
       <c r="O15">
-        <v>-20.05687847551022</v>
+        <v>-32.21533537551019</v>
       </c>
       <c r="P15">
-        <v>-60.17063542653065</v>
+        <v>-96.64600612653058</v>
       </c>
       <c r="Q15">
-        <v>683.4293645734693</v>
+        <v>646.9539938734695</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09645694879357067</v>
+        <v>0.097045983081868</v>
       </c>
       <c r="T15">
-        <v>0.9873982197158987</v>
+        <v>0.9988795943637578</v>
       </c>
       <c r="U15">
         <v>0.1186</v>
       </c>
       <c r="V15">
-        <v>0.2182764675958082</v>
+        <v>0.2026852913389648</v>
       </c>
       <c r="W15">
-        <v>0.09271241094313716</v>
+        <v>0.09456152444719879</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.8731058703832327</v>
+        <v>0.8107411653558592</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2804,22 +2804,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09669815887301432</v>
+        <v>0.1102830469830188</v>
       </c>
       <c r="C16">
-        <v>29977.583586289</v>
+        <v>22139.17910447103</v>
       </c>
       <c r="D16">
-        <v>35259.907586289</v>
+        <v>27831.56910447104</v>
       </c>
       <c r="E16">
-        <v>2485.824</v>
+        <v>2895.890000000001</v>
       </c>
       <c r="F16">
-        <v>5740.924</v>
+        <v>6150.990000000001</v>
       </c>
       <c r="G16">
         <v>458.6</v>
@@ -2840,45 +2840,45 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M16">
-        <v>680.8735864</v>
+        <v>1235.118792</v>
       </c>
       <c r="N16">
-        <v>-128.8613415020408</v>
+        <v>-683.106547102041</v>
       </c>
       <c r="O16">
-        <v>-32.21533537551019</v>
+        <v>-170.7766367755102</v>
       </c>
       <c r="P16">
-        <v>-96.64600612653058</v>
+        <v>-512.3299103265307</v>
       </c>
       <c r="Q16">
-        <v>646.9539938734695</v>
+        <v>231.2700896734693</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.097045983081868</v>
+        <v>0.0982687453651894</v>
       </c>
       <c r="T16">
-        <v>0.9988795943637578</v>
+        <v>1.022713507191933</v>
       </c>
       <c r="U16">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.2026852913389648</v>
+        <v>0.1117326220913735</v>
       </c>
       <c r="W16">
-        <v>0.09456152444719879</v>
+        <v>0.1783640894840522</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y16">
-        <v>0.8107411653558592</v>
+        <v>0.4469304883654941</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2886,22 +2886,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1102830469830188</v>
+        <v>0.1118330469830188</v>
       </c>
       <c r="C17">
-        <v>22139.17910447103</v>
+        <v>21075.82003254866</v>
       </c>
       <c r="D17">
-        <v>27831.56910447104</v>
+        <v>27178.27603254866</v>
       </c>
       <c r="E17">
-        <v>2895.89</v>
+        <v>3305.956</v>
       </c>
       <c r="F17">
-        <v>6150.99</v>
+        <v>6561.056</v>
       </c>
       <c r="G17">
         <v>458.6</v>
@@ -2922,37 +2922,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M17">
-        <v>1235.118792</v>
+        <v>1317.4600448</v>
       </c>
       <c r="N17">
-        <v>-683.1065471020407</v>
+        <v>-765.4477999020406</v>
       </c>
       <c r="O17">
-        <v>-170.7766367755102</v>
+        <v>-191.3619499755102</v>
       </c>
       <c r="P17">
-        <v>-512.3299103265306</v>
+        <v>-574.0858499265305</v>
       </c>
       <c r="Q17">
-        <v>231.2700896734694</v>
+        <v>169.5141500734695</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0982687453651894</v>
+        <v>0.09889337328620357</v>
       </c>
       <c r="T17">
-        <v>1.022713507191933</v>
+        <v>1.034888667991837</v>
       </c>
       <c r="U17">
         <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.1117326220913736</v>
+        <v>0.1047493332106627</v>
       </c>
       <c r="W17">
-        <v>0.1783640894840522</v>
+        <v>0.1797663338912989</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.4469304883654942</v>
+        <v>0.4189973328426508</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2968,22 +2968,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1118330469830188</v>
+        <v>0.1133830469830188</v>
       </c>
       <c r="C18">
-        <v>21075.82003254866</v>
+        <v>20042.42718164425</v>
       </c>
       <c r="D18">
-        <v>27178.27603254866</v>
+        <v>26554.94918164425</v>
       </c>
       <c r="E18">
-        <v>3305.956</v>
+        <v>3716.022</v>
       </c>
       <c r="F18">
-        <v>6561.056</v>
+        <v>6971.122</v>
       </c>
       <c r="G18">
         <v>458.6</v>
@@ -3004,37 +3004,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M18">
-        <v>1317.4600448</v>
+        <v>1399.8012976</v>
       </c>
       <c r="N18">
-        <v>-765.4477999020406</v>
+        <v>-847.7890527020407</v>
       </c>
       <c r="O18">
-        <v>-191.3619499755102</v>
+        <v>-211.9472631755102</v>
       </c>
       <c r="P18">
-        <v>-574.0858499265305</v>
+        <v>-635.8417895265305</v>
       </c>
       <c r="Q18">
-        <v>169.5141500734695</v>
+        <v>107.7582104734695</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09889337328620357</v>
+        <v>0.09953305248242289</v>
       </c>
       <c r="T18">
-        <v>1.034888667991837</v>
+        <v>1.047357206160414</v>
       </c>
       <c r="U18">
         <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.1047493332106627</v>
+        <v>0.09858760772768255</v>
       </c>
       <c r="W18">
-        <v>0.1797663338912989</v>
+        <v>0.1810036083682813</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.4189973328426508</v>
+        <v>0.3943504309107302</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3050,22 +3050,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1133830469830188</v>
+        <v>0.1149330469830188</v>
       </c>
       <c r="C19">
-        <v>20042.42718164425</v>
+        <v>19036.98497550568</v>
       </c>
       <c r="D19">
-        <v>26554.94918164425</v>
+        <v>25959.57297550569</v>
       </c>
       <c r="E19">
-        <v>3716.022</v>
+        <v>4126.088000000002</v>
       </c>
       <c r="F19">
-        <v>6971.122</v>
+        <v>7381.188000000001</v>
       </c>
       <c r="G19">
         <v>458.6</v>
@@ -3086,37 +3086,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M19">
-        <v>1399.8012976</v>
+        <v>1482.1425504</v>
       </c>
       <c r="N19">
-        <v>-847.7890527020407</v>
+        <v>-930.1303055020411</v>
       </c>
       <c r="O19">
-        <v>-211.9472631755102</v>
+        <v>-232.5325763755103</v>
       </c>
       <c r="P19">
-        <v>-635.8417895265305</v>
+        <v>-697.5977291265308</v>
       </c>
       <c r="Q19">
-        <v>107.7582104734695</v>
+        <v>46.00227087346923</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09953305248242289</v>
+        <v>0.1001883336102573</v>
       </c>
       <c r="T19">
-        <v>1.047357206160414</v>
+        <v>1.060129855016028</v>
       </c>
       <c r="U19">
         <v>0.2008</v>
       </c>
       <c r="V19">
-        <v>0.09858760772768255</v>
+        <v>0.09311051840947794</v>
       </c>
       <c r="W19">
-        <v>0.1810036083682813</v>
+        <v>0.1821034079033768</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.3943504309107302</v>
+        <v>0.3724420736379117</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3132,22 +3132,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1149330469830188</v>
+        <v>0.1164830469830188</v>
       </c>
       <c r="C20">
-        <v>19036.98497550569</v>
+        <v>18057.65463519364</v>
       </c>
       <c r="D20">
-        <v>25959.57297550569</v>
+        <v>25390.30863519364</v>
       </c>
       <c r="E20">
-        <v>4126.088</v>
+        <v>4536.154</v>
       </c>
       <c r="F20">
-        <v>7381.187999999999</v>
+        <v>7791.254</v>
       </c>
       <c r="G20">
         <v>458.6</v>
@@ -3168,37 +3168,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M20">
-        <v>1482.1425504</v>
+        <v>1564.4838032</v>
       </c>
       <c r="N20">
-        <v>-930.1303055020406</v>
+        <v>-1012.471558302041</v>
       </c>
       <c r="O20">
-        <v>-232.5325763755102</v>
+        <v>-253.1178895755102</v>
       </c>
       <c r="P20">
-        <v>-697.5977291265305</v>
+        <v>-759.3536687265306</v>
       </c>
       <c r="Q20">
-        <v>46.00227087346957</v>
+        <v>-15.75366872653058</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1001883336102573</v>
+        <v>0.1008597945190259</v>
       </c>
       <c r="T20">
-        <v>1.060129855016028</v>
+        <v>1.073217877917461</v>
       </c>
       <c r="U20">
         <v>0.2008</v>
       </c>
       <c r="V20">
-        <v>0.09311051840947797</v>
+        <v>0.08820996480897912</v>
       </c>
       <c r="W20">
-        <v>0.1821034079033768</v>
+        <v>0.183087439066357</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3724420736379118</v>
+        <v>0.3528398592359164</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3214,22 +3214,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1164830469830188</v>
+        <v>0.1180330469830188</v>
       </c>
       <c r="C21">
-        <v>18057.65463519364</v>
+        <v>17102.75521021293</v>
       </c>
       <c r="D21">
-        <v>25390.30863519364</v>
+        <v>24845.47521021293</v>
       </c>
       <c r="E21">
-        <v>4536.154</v>
+        <v>4946.219999999999</v>
       </c>
       <c r="F21">
-        <v>7791.254</v>
+        <v>8201.32</v>
       </c>
       <c r="G21">
         <v>458.6</v>
@@ -3250,37 +3250,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M21">
-        <v>1564.4838032</v>
+        <v>1646.825056</v>
       </c>
       <c r="N21">
-        <v>-1012.471558302041</v>
+        <v>-1094.812811102041</v>
       </c>
       <c r="O21">
-        <v>-253.1178895755102</v>
+        <v>-273.7032027755101</v>
       </c>
       <c r="P21">
-        <v>-759.3536687265306</v>
+        <v>-821.1096083265304</v>
       </c>
       <c r="Q21">
-        <v>-15.75366872653058</v>
+        <v>-77.50960832653038</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1008597945190259</v>
+        <v>0.1015480419505138</v>
       </c>
       <c r="T21">
-        <v>1.073217877917461</v>
+        <v>1.086633101391429</v>
       </c>
       <c r="U21">
         <v>0.2008</v>
       </c>
       <c r="V21">
-        <v>0.08820996480897912</v>
+        <v>0.08379946656853017</v>
       </c>
       <c r="W21">
-        <v>0.183087439066357</v>
+        <v>0.1839730671130392</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3528398592359164</v>
+        <v>0.3351978662741207</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3296,22 +3296,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1180330469830188</v>
+        <v>0.1195830469830188</v>
       </c>
       <c r="C22">
-        <v>17102.75521021293</v>
+        <v>16170.74700057915</v>
       </c>
       <c r="D22">
-        <v>24845.47521021293</v>
+        <v>24323.53300057915</v>
       </c>
       <c r="E22">
-        <v>4946.219999999999</v>
+        <v>5356.286</v>
       </c>
       <c r="F22">
-        <v>8201.32</v>
+        <v>8611.386</v>
       </c>
       <c r="G22">
         <v>458.6</v>
@@ -3332,37 +3332,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M22">
-        <v>1646.825056</v>
+        <v>1729.1663088</v>
       </c>
       <c r="N22">
-        <v>-1094.812811102041</v>
+        <v>-1177.154063902041</v>
       </c>
       <c r="O22">
-        <v>-273.7032027755101</v>
+        <v>-294.2885159755102</v>
       </c>
       <c r="P22">
-        <v>-821.1096083265304</v>
+        <v>-882.8655479265307</v>
       </c>
       <c r="Q22">
-        <v>-77.50960832653038</v>
+        <v>-139.2655479265306</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1015480419505138</v>
+        <v>0.1022537133676089</v>
       </c>
       <c r="T22">
-        <v>1.086633101391429</v>
+        <v>1.10038795077613</v>
       </c>
       <c r="U22">
         <v>0.2008</v>
       </c>
       <c r="V22">
-        <v>0.08379946656853017</v>
+        <v>0.07980901577955253</v>
       </c>
       <c r="W22">
-        <v>0.1839730671130392</v>
+        <v>0.1847743496314659</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3351978662741207</v>
+        <v>0.3192360631182102</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3378,22 +3378,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1195830469830188</v>
+        <v>0.1211330469830188</v>
       </c>
       <c r="C23">
-        <v>16170.74700057915</v>
+        <v>15260.21702546082</v>
       </c>
       <c r="D23">
-        <v>24323.53300057915</v>
+        <v>23823.06902546082</v>
       </c>
       <c r="E23">
-        <v>5356.285999999998</v>
+        <v>5766.351999999999</v>
       </c>
       <c r="F23">
-        <v>8611.385999999999</v>
+        <v>9021.451999999999</v>
       </c>
       <c r="G23">
         <v>458.6</v>
@@ -3414,37 +3414,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M23">
-        <v>1729.1663088</v>
+        <v>1811.5075616</v>
       </c>
       <c r="N23">
-        <v>-1177.15406390204</v>
+        <v>-1259.495316702041</v>
       </c>
       <c r="O23">
-        <v>-294.2885159755101</v>
+        <v>-314.8738291755102</v>
       </c>
       <c r="P23">
-        <v>-882.8655479265303</v>
+        <v>-944.6214875265306</v>
       </c>
       <c r="Q23">
-        <v>-139.2655479265303</v>
+        <v>-201.0214875265306</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1022537133676089</v>
+        <v>0.1029774789236038</v>
       </c>
       <c r="T23">
-        <v>1.10038795077613</v>
+        <v>1.114495488606594</v>
       </c>
       <c r="U23">
         <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.07980901577955254</v>
+        <v>0.07618133324411833</v>
       </c>
       <c r="W23">
-        <v>0.1847743496314659</v>
+        <v>0.185502788284581</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3192360631182103</v>
+        <v>0.3047253329764733</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3460,22 +3460,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1211330469830188</v>
+        <v>0.1226830469830188</v>
       </c>
       <c r="C24">
-        <v>15260.21702546082</v>
+        <v>14369.86624957752</v>
       </c>
       <c r="D24">
-        <v>23823.06902546082</v>
+        <v>23342.78424957752</v>
       </c>
       <c r="E24">
-        <v>5766.351999999999</v>
+        <v>6176.418</v>
       </c>
       <c r="F24">
-        <v>9021.451999999999</v>
+        <v>9431.518</v>
       </c>
       <c r="G24">
         <v>458.6</v>
@@ -3496,37 +3496,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M24">
-        <v>1811.5075616</v>
+        <v>1893.8488144</v>
       </c>
       <c r="N24">
-        <v>-1259.495316702041</v>
+        <v>-1341.836569502041</v>
       </c>
       <c r="O24">
-        <v>-314.8738291755102</v>
+        <v>-335.4591423755102</v>
       </c>
       <c r="P24">
-        <v>-944.6214875265306</v>
+        <v>-1006.377427126531</v>
       </c>
       <c r="Q24">
-        <v>-201.0214875265306</v>
+        <v>-262.7774271265305</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1029774789236038</v>
+        <v>0.1037200435849494</v>
       </c>
       <c r="T24">
-        <v>1.114495488606594</v>
+        <v>1.128969455991095</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.07618133324411833</v>
+        <v>0.07286910136393927</v>
       </c>
       <c r="W24">
-        <v>0.185502788284581</v>
+        <v>0.186167884446121</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3047253329764733</v>
+        <v>0.2914764054557571</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3542,22 +3542,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1226830469830188</v>
+        <v>0.1242330469830188</v>
       </c>
       <c r="C25">
-        <v>14369.86624957752</v>
+        <v>13498.49832419549</v>
       </c>
       <c r="D25">
-        <v>23342.78424957752</v>
+        <v>22881.48232419549</v>
       </c>
       <c r="E25">
-        <v>6176.418</v>
+        <v>6586.484</v>
       </c>
       <c r="F25">
-        <v>9431.518</v>
+        <v>9841.584000000001</v>
       </c>
       <c r="G25">
         <v>458.6</v>
@@ -3578,37 +3578,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M25">
-        <v>1893.8488144</v>
+        <v>1976.1900672</v>
       </c>
       <c r="N25">
-        <v>-1341.836569502041</v>
+        <v>-1424.177822302041</v>
       </c>
       <c r="O25">
-        <v>-335.4591423755102</v>
+        <v>-356.0444555755103</v>
       </c>
       <c r="P25">
-        <v>-1006.377427126531</v>
+        <v>-1068.133366726531</v>
       </c>
       <c r="Q25">
-        <v>-262.7774271265305</v>
+        <v>-324.5333667265307</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1037200435849494</v>
+        <v>0.1044821494215934</v>
       </c>
       <c r="T25">
-        <v>1.128969455991095</v>
+        <v>1.143824317254136</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.07286910136393927</v>
+        <v>0.06983288880710846</v>
       </c>
       <c r="W25">
-        <v>0.186167884446121</v>
+        <v>0.1867775559275326</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2914764054557571</v>
+        <v>0.2793315552284338</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3624,22 +3624,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1242330469830188</v>
+        <v>0.1257830469830188</v>
       </c>
       <c r="C26">
-        <v>13498.4983241955</v>
+        <v>12645.00963725995</v>
       </c>
       <c r="D26">
-        <v>22881.4823241955</v>
+        <v>22438.05963725995</v>
       </c>
       <c r="E26">
-        <v>6586.483999999999</v>
+        <v>6996.549999999999</v>
       </c>
       <c r="F26">
-        <v>9841.583999999999</v>
+        <v>10251.65</v>
       </c>
       <c r="G26">
         <v>458.6</v>
@@ -3660,37 +3660,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M26">
-        <v>1976.1900672</v>
+        <v>2058.53132</v>
       </c>
       <c r="N26">
-        <v>-1424.177822302041</v>
+        <v>-1506.519075102041</v>
       </c>
       <c r="O26">
-        <v>-356.0444555755101</v>
+        <v>-376.6297687755102</v>
       </c>
       <c r="P26">
-        <v>-1068.13336672653</v>
+        <v>-1129.889306326531</v>
       </c>
       <c r="Q26">
-        <v>-324.5333667265303</v>
+        <v>-386.2893063265307</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1044821494215934</v>
+        <v>0.105264578080548</v>
       </c>
       <c r="T26">
-        <v>1.143824317254136</v>
+        <v>1.159075308150858</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.06983288880710847</v>
+        <v>0.06703957325482413</v>
       </c>
       <c r="W26">
-        <v>0.1867775559275326</v>
+        <v>0.1873384536904313</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2793315552284339</v>
+        <v>0.2681582930192965</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3706,22 +3706,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1257830469830188</v>
+        <v>0.1273330469830188</v>
       </c>
       <c r="C27">
-        <v>12645.00963725995</v>
+        <v>11808.38049845076</v>
       </c>
       <c r="D27">
-        <v>22438.05963725995</v>
+        <v>22011.49649845076</v>
       </c>
       <c r="E27">
-        <v>6996.549999999999</v>
+        <v>7406.616</v>
       </c>
       <c r="F27">
-        <v>10251.65</v>
+        <v>10661.716</v>
       </c>
       <c r="G27">
         <v>458.6</v>
@@ -3742,37 +3742,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M27">
-        <v>2058.53132</v>
+        <v>2140.8725728</v>
       </c>
       <c r="N27">
-        <v>-1506.519075102041</v>
+        <v>-1588.860327902041</v>
       </c>
       <c r="O27">
-        <v>-376.6297687755102</v>
+        <v>-397.2150819755102</v>
       </c>
       <c r="P27">
-        <v>-1129.889306326531</v>
+        <v>-1191.645245926531</v>
       </c>
       <c r="Q27">
-        <v>-386.2893063265307</v>
+        <v>-448.0452459265306</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.105264578080548</v>
+        <v>0.1060681534600149</v>
       </c>
       <c r="T27">
-        <v>1.159075308150858</v>
+        <v>1.174738487990734</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.06703957325482413</v>
+        <v>0.06446112812963858</v>
       </c>
       <c r="W27">
-        <v>0.1873384536904313</v>
+        <v>0.1878562054715686</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2681582930192965</v>
+        <v>0.2578445125185543</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3788,22 +3788,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1273330469830188</v>
+        <v>0.1288830469830188</v>
       </c>
       <c r="C28">
-        <v>11808.38049845076</v>
+        <v>10987.66731094965</v>
       </c>
       <c r="D28">
-        <v>22011.49649845076</v>
+        <v>21600.84931094966</v>
       </c>
       <c r="E28">
-        <v>7406.616</v>
+        <v>7816.682000000001</v>
       </c>
       <c r="F28">
-        <v>10661.716</v>
+        <v>11071.782</v>
       </c>
       <c r="G28">
         <v>458.6</v>
@@ -3824,37 +3824,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M28">
-        <v>2140.8725728</v>
+        <v>2223.2138256</v>
       </c>
       <c r="N28">
-        <v>-1588.860327902041</v>
+        <v>-1671.201580702041</v>
       </c>
       <c r="O28">
-        <v>-397.2150819755102</v>
+        <v>-417.8003951755103</v>
       </c>
       <c r="P28">
-        <v>-1191.645245926531</v>
+        <v>-1253.401185526531</v>
       </c>
       <c r="Q28">
-        <v>-448.0452459265306</v>
+        <v>-509.8011855265307</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1060681534600149</v>
+        <v>0.1068937446033027</v>
       </c>
       <c r="T28">
-        <v>1.174738487990734</v>
+        <v>1.190830796045402</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.06446112812963858</v>
+        <v>0.06207367893965196</v>
       </c>
       <c r="W28">
-        <v>0.1878562054715686</v>
+        <v>0.1883356052689179</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2578445125185543</v>
+        <v>0.2482947157586078</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3870,22 +3870,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1288830469830188</v>
+        <v>0.1304330469830188</v>
       </c>
       <c r="C29">
-        <v>10987.66731094965</v>
+        <v>10181.9956034216</v>
       </c>
       <c r="D29">
-        <v>21600.84931094966</v>
+        <v>21205.2436034216</v>
       </c>
       <c r="E29">
-        <v>7816.682000000001</v>
+        <v>8226.748</v>
       </c>
       <c r="F29">
-        <v>11071.782</v>
+        <v>11481.848</v>
       </c>
       <c r="G29">
         <v>458.6</v>
@@ -3906,37 +3906,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M29">
-        <v>2223.2138256</v>
+        <v>2305.5550784</v>
       </c>
       <c r="N29">
-        <v>-1671.201580702041</v>
+        <v>-1753.542833502041</v>
       </c>
       <c r="O29">
-        <v>-417.8003951755103</v>
+        <v>-438.3857083755103</v>
       </c>
       <c r="P29">
-        <v>-1253.401185526531</v>
+        <v>-1315.157125126531</v>
       </c>
       <c r="Q29">
-        <v>-509.8011855265307</v>
+        <v>-571.5571251265309</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1068937446033027</v>
+        <v>0.1077422688339042</v>
       </c>
       <c r="T29">
-        <v>1.190830796045402</v>
+        <v>1.207370112657143</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.06207367893965196</v>
+        <v>0.05985676183466439</v>
       </c>
       <c r="W29">
-        <v>0.1883356052689179</v>
+        <v>0.1887807622235994</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2482947157586078</v>
+        <v>0.2394270473386575</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3952,22 +3952,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1304330469830188</v>
+        <v>0.1319830469830188</v>
       </c>
       <c r="C30">
-        <v>10181.9956034216</v>
+        <v>9390.55381391419</v>
       </c>
       <c r="D30">
-        <v>21205.2436034216</v>
+        <v>20823.86781391419</v>
       </c>
       <c r="E30">
-        <v>8226.748</v>
+        <v>8636.814</v>
       </c>
       <c r="F30">
-        <v>11481.848</v>
+        <v>11891.914</v>
       </c>
       <c r="G30">
         <v>458.6</v>
@@ -3988,37 +3988,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M30">
-        <v>2305.5550784</v>
+        <v>2387.8963312</v>
       </c>
       <c r="N30">
-        <v>-1753.542833502041</v>
+        <v>-1835.884086302041</v>
       </c>
       <c r="O30">
-        <v>-438.3857083755103</v>
+        <v>-458.9710215755102</v>
       </c>
       <c r="P30">
-        <v>-1315.157125126531</v>
+        <v>-1376.913064726531</v>
       </c>
       <c r="Q30">
-        <v>-571.5571251265309</v>
+        <v>-633.3130647265306</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1077422688339042</v>
+        <v>0.1086146951555085</v>
       </c>
       <c r="T30">
-        <v>1.207370112657143</v>
+        <v>1.224375325511469</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.05985676183466439</v>
+        <v>0.05779273556450356</v>
       </c>
       <c r="W30">
-        <v>0.1887807622235994</v>
+        <v>0.1891952186986477</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2394270473386575</v>
+        <v>0.2311709422580142</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4034,22 +4034,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1319830469830188</v>
+        <v>0.1335330469830188</v>
       </c>
       <c r="C31">
-        <v>9390.553813914192</v>
+        <v>8612.587732684657</v>
       </c>
       <c r="D31">
-        <v>20823.86781391419</v>
+        <v>20455.96773268466</v>
       </c>
       <c r="E31">
-        <v>8636.813999999998</v>
+        <v>9046.879999999999</v>
       </c>
       <c r="F31">
-        <v>11891.914</v>
+        <v>12301.98</v>
       </c>
       <c r="G31">
         <v>458.6</v>
@@ -4070,37 +4070,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M31">
-        <v>2387.8963312</v>
+        <v>2470.237584</v>
       </c>
       <c r="N31">
-        <v>-1835.88408630204</v>
+        <v>-1918.225339102041</v>
       </c>
       <c r="O31">
-        <v>-458.9710215755101</v>
+        <v>-479.5563347755102</v>
       </c>
       <c r="P31">
-        <v>-1376.91306472653</v>
+        <v>-1438.669004326531</v>
       </c>
       <c r="Q31">
-        <v>-633.3130647265303</v>
+        <v>-695.0690043265307</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1086146951555085</v>
+        <v>0.1095120479434443</v>
       </c>
       <c r="T31">
-        <v>1.224375325511469</v>
+        <v>1.241866401590205</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.05779273556450357</v>
+        <v>0.05586631104568678</v>
       </c>
       <c r="W31">
-        <v>0.1891952186986477</v>
+        <v>0.1895820447420261</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2311709422580143</v>
+        <v>0.223465244182747</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4116,22 +4116,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1335330469830188</v>
+        <v>0.1350830469830188</v>
       </c>
       <c r="C32">
-        <v>8612.587732684657</v>
+        <v>7847.395523879402</v>
       </c>
       <c r="D32">
-        <v>20455.96773268466</v>
+        <v>20100.8415238794</v>
       </c>
       <c r="E32">
-        <v>9046.879999999999</v>
+        <v>9456.946</v>
       </c>
       <c r="F32">
-        <v>12301.98</v>
+        <v>12712.046</v>
       </c>
       <c r="G32">
         <v>458.6</v>
@@ -4152,37 +4152,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M32">
-        <v>2470.237584</v>
+        <v>2552.5788368</v>
       </c>
       <c r="N32">
-        <v>-1918.225339102041</v>
+        <v>-2000.566591902041</v>
       </c>
       <c r="O32">
-        <v>-479.5563347755102</v>
+        <v>-500.1416479755103</v>
       </c>
       <c r="P32">
-        <v>-1438.669004326531</v>
+        <v>-1500.424943926531</v>
       </c>
       <c r="Q32">
-        <v>-695.0690043265307</v>
+        <v>-756.8249439265309</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1095120479434443</v>
+        <v>0.1104354109571174</v>
       </c>
       <c r="T32">
-        <v>1.241866401590205</v>
+        <v>1.259864465381367</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.05586631104568678</v>
+        <v>0.05406417197969687</v>
       </c>
       <c r="W32">
-        <v>0.1895820447420261</v>
+        <v>0.1899439142664769</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.223465244182747</v>
+        <v>0.2162566879187875</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4198,22 +4198,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1350830469830188</v>
+        <v>0.1366330469830188</v>
       </c>
       <c r="C33">
-        <v>7847.395523879402</v>
+        <v>7094.323256921985</v>
       </c>
       <c r="D33">
-        <v>20100.8415238794</v>
+        <v>19757.83525692199</v>
       </c>
       <c r="E33">
-        <v>9456.946</v>
+        <v>9867.011999999999</v>
       </c>
       <c r="F33">
-        <v>12712.046</v>
+        <v>13122.112</v>
       </c>
       <c r="G33">
         <v>458.6</v>
@@ -4234,37 +4234,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M33">
-        <v>2552.5788368</v>
+        <v>2634.9200896</v>
       </c>
       <c r="N33">
-        <v>-2000.566591902041</v>
+        <v>-2082.907844702041</v>
       </c>
       <c r="O33">
-        <v>-500.1416479755103</v>
+        <v>-520.7269611755102</v>
       </c>
       <c r="P33">
-        <v>-1500.424943926531</v>
+        <v>-1562.180883526531</v>
       </c>
       <c r="Q33">
-        <v>-756.8249439265309</v>
+        <v>-818.5808835265306</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1104354109571174</v>
+        <v>0.1113859317064868</v>
       </c>
       <c r="T33">
-        <v>1.259864465381367</v>
+        <v>1.278391883989916</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.05406417197969687</v>
+        <v>0.05237466660533135</v>
       </c>
       <c r="W33">
-        <v>0.1899439142664769</v>
+        <v>0.1902831669456495</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2162566879187875</v>
+        <v>0.2094986664213254</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4280,22 +4280,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1366330469830188</v>
+        <v>0.1381830469830189</v>
       </c>
       <c r="C34">
-        <v>7094.323256921985</v>
+        <v>6352.760887746594</v>
       </c>
       <c r="D34">
-        <v>19757.83525692199</v>
+        <v>19426.33888774659</v>
       </c>
       <c r="E34">
-        <v>9867.011999999999</v>
+        <v>10277.078</v>
       </c>
       <c r="F34">
-        <v>13122.112</v>
+        <v>13532.178</v>
       </c>
       <c r="G34">
         <v>458.6</v>
@@ -4316,37 +4316,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M34">
-        <v>2634.9200896</v>
+        <v>2717.2613424</v>
       </c>
       <c r="N34">
-        <v>-2082.907844702041</v>
+        <v>-2165.249097502041</v>
       </c>
       <c r="O34">
-        <v>-520.7269611755102</v>
+        <v>-541.3122743755102</v>
       </c>
       <c r="P34">
-        <v>-1562.180883526531</v>
+        <v>-1623.936823126531</v>
       </c>
       <c r="Q34">
-        <v>-818.5808835265306</v>
+        <v>-880.3368231265307</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1113859317064868</v>
+        <v>0.1123648262095687</v>
       </c>
       <c r="T34">
-        <v>1.278391883989916</v>
+        <v>1.297472359870363</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.05237466660533135</v>
+        <v>0.05078755549607888</v>
       </c>
       <c r="W34">
-        <v>0.1902831669456495</v>
+        <v>0.1906018588563874</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2094986664213254</v>
+        <v>0.2031502219843155</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4362,22 +4362,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1381830469830189</v>
+        <v>0.1517458850176758</v>
       </c>
       <c r="C35">
-        <v>6352.760887746594</v>
+        <v>3455.799923426772</v>
       </c>
       <c r="D35">
-        <v>19426.33888774659</v>
+        <v>16939.44392342677</v>
       </c>
       <c r="E35">
-        <v>10277.078</v>
+        <v>10687.144</v>
       </c>
       <c r="F35">
-        <v>13532.178</v>
+        <v>13942.244</v>
       </c>
       <c r="G35">
         <v>458.6</v>
@@ -4398,45 +4398,45 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M35">
-        <v>2717.2613424</v>
+        <v>3287.5811352</v>
       </c>
       <c r="N35">
-        <v>-2165.249097502041</v>
+        <v>-2735.568890302041</v>
       </c>
       <c r="O35">
-        <v>-541.3122743755102</v>
+        <v>-683.8922225755102</v>
       </c>
       <c r="P35">
-        <v>-1623.936823126531</v>
+        <v>-2051.67666772653</v>
       </c>
       <c r="Q35">
-        <v>-880.3368231265307</v>
+        <v>-1308.076667726531</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1123648262095687</v>
+        <v>0.1135443509016182</v>
       </c>
       <c r="T35">
-        <v>1.297472359870363</v>
+        <v>1.320463491566564</v>
       </c>
       <c r="U35">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.05078755549607888</v>
+        <v>0.04197708149219392</v>
       </c>
       <c r="W35">
-        <v>0.1906018588563874</v>
+        <v>0.2259018041841407</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.2031502219843155</v>
+        <v>0.1679083259687757</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4444,22 +4444,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1517458850176758</v>
+        <v>0.1536458850176758</v>
       </c>
       <c r="C36">
-        <v>3455.799923426772</v>
+        <v>2747.29932437613</v>
       </c>
       <c r="D36">
-        <v>16939.44392342677</v>
+        <v>16641.00932437613</v>
       </c>
       <c r="E36">
-        <v>10687.144</v>
+        <v>11097.21</v>
       </c>
       <c r="F36">
-        <v>13942.244</v>
+        <v>14352.31</v>
       </c>
       <c r="G36">
         <v>458.6</v>
@@ -4480,37 +4480,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M36">
-        <v>3287.5811352</v>
+        <v>3384.274698000001</v>
       </c>
       <c r="N36">
-        <v>-2735.568890302041</v>
+        <v>-2832.262453102041</v>
       </c>
       <c r="O36">
-        <v>-683.8922225755102</v>
+        <v>-708.0656132755104</v>
       </c>
       <c r="P36">
-        <v>-2051.67666772653</v>
+        <v>-2124.196839826531</v>
       </c>
       <c r="Q36">
-        <v>-1308.076667726531</v>
+        <v>-1380.596839826531</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1135443509016182</v>
+        <v>0.11458657168472</v>
       </c>
       <c r="T36">
-        <v>1.320463491566564</v>
+        <v>1.340778314513742</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.04197708149219392</v>
+        <v>0.04077773630670267</v>
       </c>
       <c r="W36">
-        <v>0.2259018041841407</v>
+        <v>0.2261846097788795</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1679083259687757</v>
+        <v>0.1631109452268106</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4526,22 +4526,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1536458850176758</v>
+        <v>0.1555458850176759</v>
       </c>
       <c r="C37">
-        <v>2747.29932437613</v>
+        <v>2049.132155833709</v>
       </c>
       <c r="D37">
-        <v>16641.00932437613</v>
+        <v>16352.90815583371</v>
       </c>
       <c r="E37">
-        <v>11097.21</v>
+        <v>11507.276</v>
       </c>
       <c r="F37">
-        <v>14352.31</v>
+        <v>14762.376</v>
       </c>
       <c r="G37">
         <v>458.6</v>
@@ -4562,37 +4562,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M37">
-        <v>3384.274698000001</v>
+        <v>3480.968260800001</v>
       </c>
       <c r="N37">
-        <v>-2832.262453102041</v>
+        <v>-2928.956015902042</v>
       </c>
       <c r="O37">
-        <v>-708.0656132755104</v>
+        <v>-732.2390039755104</v>
       </c>
       <c r="P37">
-        <v>-2124.196839826531</v>
+        <v>-2196.717011926531</v>
       </c>
       <c r="Q37">
-        <v>-1380.596839826531</v>
+        <v>-1453.117011926531</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.11458657168472</v>
+        <v>0.1156613618672938</v>
       </c>
       <c r="T37">
-        <v>1.340778314513742</v>
+        <v>1.361727975678019</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.04077773630670267</v>
+        <v>0.03964502140929425</v>
       </c>
       <c r="W37">
-        <v>0.2261846097788795</v>
+        <v>0.2264517039516884</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1631109452268106</v>
+        <v>0.158580085637177</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4608,22 +4608,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1555458850176759</v>
+        <v>0.1574458850176759</v>
       </c>
       <c r="C38">
-        <v>2049.132155833713</v>
+        <v>1360.770851970385</v>
       </c>
       <c r="D38">
-        <v>16352.90815583371</v>
+        <v>16074.61285197038</v>
       </c>
       <c r="E38">
-        <v>11507.276</v>
+        <v>11917.342</v>
       </c>
       <c r="F38">
-        <v>14762.376</v>
+        <v>15172.442</v>
       </c>
       <c r="G38">
         <v>458.6</v>
@@ -4644,37 +4644,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M38">
-        <v>3480.9682608</v>
+        <v>3577.6618236</v>
       </c>
       <c r="N38">
-        <v>-2928.956015902041</v>
+        <v>-3025.649578702041</v>
       </c>
       <c r="O38">
-        <v>-732.2390039755102</v>
+        <v>-756.4123946755102</v>
       </c>
       <c r="P38">
-        <v>-2196.717011926531</v>
+        <v>-2269.23718402653</v>
       </c>
       <c r="Q38">
-        <v>-1453.117011926531</v>
+        <v>-1525.637184026531</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1156613618672938</v>
+        <v>0.1167702723731238</v>
       </c>
       <c r="T38">
-        <v>1.361727975678019</v>
+        <v>1.383342705450686</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03964502140929426</v>
+        <v>0.0385735343441782</v>
       </c>
       <c r="W38">
-        <v>0.2264517039516884</v>
+        <v>0.2267043606016428</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1585800856371771</v>
+        <v>0.1542941373767128</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4690,22 +4690,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1574458850176759</v>
+        <v>0.1593458850176759</v>
       </c>
       <c r="C39">
-        <v>1360.770851970385</v>
+        <v>681.7231586752969</v>
       </c>
       <c r="D39">
-        <v>16074.61285197038</v>
+        <v>15805.6311586753</v>
       </c>
       <c r="E39">
-        <v>11917.342</v>
+        <v>12327.408</v>
       </c>
       <c r="F39">
-        <v>15172.442</v>
+        <v>15582.508</v>
       </c>
       <c r="G39">
         <v>458.6</v>
@@ -4726,37 +4726,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M39">
-        <v>3577.6618236</v>
+        <v>3674.3553864</v>
       </c>
       <c r="N39">
-        <v>-3025.649578702041</v>
+        <v>-3122.343141502041</v>
       </c>
       <c r="O39">
-        <v>-756.4123946755102</v>
+        <v>-780.5857853755102</v>
       </c>
       <c r="P39">
-        <v>-2269.23718402653</v>
+        <v>-2341.757356126531</v>
       </c>
       <c r="Q39">
-        <v>-1525.637184026531</v>
+        <v>-1598.157356126531</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1167702723731238</v>
+        <v>0.1179149541855936</v>
       </c>
       <c r="T39">
-        <v>1.383342705450686</v>
+        <v>1.405654684570858</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.0385735343441782</v>
+        <v>0.03755844133512088</v>
       </c>
       <c r="W39">
-        <v>0.2267043606016428</v>
+        <v>0.2269437195331785</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1542941373767128</v>
+        <v>0.1502337653404835</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4772,22 +4772,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1593458850176759</v>
+        <v>0.1612458850176758</v>
       </c>
       <c r="C40">
-        <v>681.7231586752969</v>
+        <v>11.52922776737068</v>
       </c>
       <c r="D40">
-        <v>15805.6311586753</v>
+        <v>15545.50322776737</v>
       </c>
       <c r="E40">
-        <v>12327.408</v>
+        <v>12737.474</v>
       </c>
       <c r="F40">
-        <v>15582.508</v>
+        <v>15992.574</v>
       </c>
       <c r="G40">
         <v>458.6</v>
@@ -4808,37 +4808,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M40">
-        <v>3674.3553864</v>
+        <v>3771.0489492</v>
       </c>
       <c r="N40">
-        <v>-3122.343141502041</v>
+        <v>-3219.036704302041</v>
       </c>
       <c r="O40">
-        <v>-780.5857853755102</v>
+        <v>-804.7591760755103</v>
       </c>
       <c r="P40">
-        <v>-2341.757356126531</v>
+        <v>-2414.277528226531</v>
       </c>
       <c r="Q40">
-        <v>-1598.157356126531</v>
+        <v>-1670.677528226531</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1179149541855936</v>
+        <v>0.1190971665492918</v>
       </c>
       <c r="T40">
-        <v>1.405654684570858</v>
+        <v>1.428698203990052</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03755844133512088</v>
+        <v>0.03659540437781009</v>
       </c>
       <c r="W40">
-        <v>0.2269437195331785</v>
+        <v>0.2271708036477124</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1502337653404835</v>
+        <v>0.1463816175112403</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4854,22 +4854,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1612458850176758</v>
+        <v>0.1631458850176759</v>
       </c>
       <c r="C41">
-        <v>11.52922776737068</v>
+        <v>-650.2410064996366</v>
       </c>
       <c r="D41">
-        <v>15545.50322776737</v>
+        <v>15293.79899350036</v>
       </c>
       <c r="E41">
-        <v>12737.474</v>
+        <v>13147.54</v>
       </c>
       <c r="F41">
-        <v>15992.574</v>
+        <v>16402.64</v>
       </c>
       <c r="G41">
         <v>458.6</v>
@@ -4890,37 +4890,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M41">
-        <v>3771.0489492</v>
+        <v>3867.742512</v>
       </c>
       <c r="N41">
-        <v>-3219.036704302041</v>
+        <v>-3315.730267102041</v>
       </c>
       <c r="O41">
-        <v>-804.7591760755103</v>
+        <v>-828.9325667755102</v>
       </c>
       <c r="P41">
-        <v>-2414.277528226531</v>
+        <v>-2486.797700326531</v>
       </c>
       <c r="Q41">
-        <v>-1670.677528226531</v>
+        <v>-1743.197700326531</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1190971665492918</v>
+        <v>0.12031878599178</v>
       </c>
       <c r="T41">
-        <v>1.428698203990052</v>
+        <v>1.45250984072322</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03659540437781009</v>
+        <v>0.03568051926836484</v>
       </c>
       <c r="W41">
-        <v>0.2271708036477124</v>
+        <v>0.2273865335565196</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1463816175112403</v>
+        <v>0.1427220770734593</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4936,22 +4936,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1631458850176759</v>
+        <v>0.1650458850176759</v>
       </c>
       <c r="C42">
-        <v>-650.2410064996366</v>
+        <v>-1303.990200123833</v>
       </c>
       <c r="D42">
-        <v>15293.79899350036</v>
+        <v>15050.11579987617</v>
       </c>
       <c r="E42">
-        <v>13147.54</v>
+        <v>13557.606</v>
       </c>
       <c r="F42">
-        <v>16402.64</v>
+        <v>16812.706</v>
       </c>
       <c r="G42">
         <v>458.6</v>
@@ -4972,37 +4972,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M42">
-        <v>3867.742512</v>
+        <v>3964.436074800001</v>
       </c>
       <c r="N42">
-        <v>-3315.730267102041</v>
+        <v>-3412.423829902042</v>
       </c>
       <c r="O42">
-        <v>-828.9325667755102</v>
+        <v>-853.1059574755104</v>
       </c>
       <c r="P42">
-        <v>-2486.797700326531</v>
+        <v>-2559.317872426531</v>
       </c>
       <c r="Q42">
-        <v>-1743.197700326531</v>
+        <v>-1815.717872426531</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.12031878599178</v>
+        <v>0.1215818162628271</v>
       </c>
       <c r="T42">
-        <v>1.45250984072322</v>
+        <v>1.477128651582935</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.03568051926836484</v>
+        <v>0.03481026270084373</v>
       </c>
       <c r="W42">
-        <v>0.2273865335565196</v>
+        <v>0.227591740055141</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1427220770734593</v>
+        <v>0.1392410508033749</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5018,22 +5018,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1650458850176759</v>
+        <v>0.1669458850176759</v>
       </c>
       <c r="C43">
-        <v>-1303.990200123833</v>
+        <v>-1950.095748768783</v>
       </c>
       <c r="D43">
-        <v>15050.11579987617</v>
+        <v>14814.07625123122</v>
       </c>
       <c r="E43">
-        <v>13557.606</v>
+        <v>13967.672</v>
       </c>
       <c r="F43">
-        <v>16812.706</v>
+        <v>17222.772</v>
       </c>
       <c r="G43">
         <v>458.6</v>
@@ -5054,37 +5054,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M43">
-        <v>3964.436074800001</v>
+        <v>4061.1296376</v>
       </c>
       <c r="N43">
-        <v>-3412.423829902042</v>
+        <v>-3509.117392702041</v>
       </c>
       <c r="O43">
-        <v>-853.1059574755104</v>
+        <v>-877.2793481755103</v>
       </c>
       <c r="P43">
-        <v>-2559.317872426531</v>
+        <v>-2631.838044526531</v>
       </c>
       <c r="Q43">
-        <v>-1815.717872426531</v>
+        <v>-1888.238044526531</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1215818162628271</v>
+        <v>0.1228883993018414</v>
       </c>
       <c r="T43">
-        <v>1.477128651582935</v>
+        <v>1.502596386955055</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03481026270084373</v>
+        <v>0.03398144692225222</v>
       </c>
       <c r="W43">
-        <v>0.227591740055141</v>
+        <v>0.2277871748157329</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1392410508033749</v>
+        <v>0.1359257876890089</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5100,22 +5100,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1669458850176758</v>
+        <v>0.1688458850176758</v>
       </c>
       <c r="C44">
-        <v>-1950.095748768774</v>
+        <v>-2588.911738037377</v>
       </c>
       <c r="D44">
-        <v>14814.07625123122</v>
+        <v>14585.32626196262</v>
       </c>
       <c r="E44">
-        <v>13967.672</v>
+        <v>14377.738</v>
       </c>
       <c r="F44">
-        <v>17222.772</v>
+        <v>17632.838</v>
       </c>
       <c r="G44">
         <v>458.6</v>
@@ -5136,37 +5136,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M44">
-        <v>4061.1296376</v>
+        <v>4157.8232004</v>
       </c>
       <c r="N44">
-        <v>-3509.11739270204</v>
+        <v>-3605.810955502041</v>
       </c>
       <c r="O44">
-        <v>-877.2793481755101</v>
+        <v>-901.4527388755102</v>
       </c>
       <c r="P44">
-        <v>-2631.83804452653</v>
+        <v>-2704.358216626531</v>
       </c>
       <c r="Q44">
-        <v>-1888.23804452653</v>
+        <v>-1960.758216626531</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1228883993018414</v>
+        <v>0.1242408273597684</v>
       </c>
       <c r="T44">
-        <v>1.502596386955055</v>
+        <v>1.528957727077074</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03398144692225223</v>
+        <v>0.03319118071475798</v>
       </c>
       <c r="W44">
-        <v>0.2277871748157329</v>
+        <v>0.2279735195874601</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1359257876890089</v>
+        <v>0.132764722859032</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5182,22 +5182,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1688458850176758</v>
+        <v>0.1707458850176758</v>
       </c>
       <c r="C45">
-        <v>-2588.911738037377</v>
+        <v>-3220.770715803781</v>
       </c>
       <c r="D45">
-        <v>14585.32626196262</v>
+        <v>14363.53328419622</v>
       </c>
       <c r="E45">
-        <v>14377.738</v>
+        <v>14787.804</v>
       </c>
       <c r="F45">
-        <v>17632.838</v>
+        <v>18042.904</v>
       </c>
       <c r="G45">
         <v>458.6</v>
@@ -5218,37 +5218,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M45">
-        <v>4157.8232004</v>
+        <v>4254.5167632</v>
       </c>
       <c r="N45">
-        <v>-3605.810955502041</v>
+        <v>-3702.504518302041</v>
       </c>
       <c r="O45">
-        <v>-901.4527388755102</v>
+        <v>-925.6261295755103</v>
       </c>
       <c r="P45">
-        <v>-2704.358216626531</v>
+        <v>-2776.878388726531</v>
       </c>
       <c r="Q45">
-        <v>-1960.758216626531</v>
+        <v>-2033.278388726531</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1242408273597684</v>
+        <v>0.1256415564197643</v>
       </c>
       <c r="T45">
-        <v>1.528957727077074</v>
+        <v>1.556260543632021</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03319118071475798</v>
+        <v>0.03243683569851349</v>
       </c>
       <c r="W45">
-        <v>0.2279735195874601</v>
+        <v>0.2281513941422905</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.132764722859032</v>
+        <v>0.1297473427940539</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5264,22 +5264,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1707458850176758</v>
+        <v>0.1726458850176759</v>
       </c>
       <c r="C46">
-        <v>-3220.770715803781</v>
+        <v>-3845.98530526075</v>
       </c>
       <c r="D46">
-        <v>14363.53328419622</v>
+        <v>14148.38469473925</v>
       </c>
       <c r="E46">
-        <v>14787.804</v>
+        <v>15197.87</v>
       </c>
       <c r="F46">
-        <v>18042.904</v>
+        <v>18452.97</v>
       </c>
       <c r="G46">
         <v>458.6</v>
@@ -5300,37 +5300,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M46">
-        <v>4254.5167632</v>
+        <v>4351.210326</v>
       </c>
       <c r="N46">
-        <v>-3702.504518302041</v>
+        <v>-3799.198081102041</v>
       </c>
       <c r="O46">
-        <v>-925.6261295755103</v>
+        <v>-949.7995202755103</v>
       </c>
       <c r="P46">
-        <v>-2776.878388726531</v>
+        <v>-2849.398560826531</v>
       </c>
       <c r="Q46">
-        <v>-2033.278388726531</v>
+        <v>-2105.798560826531</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1256415564197643</v>
+        <v>0.1270932210819418</v>
       </c>
       <c r="T46">
-        <v>1.556260543632021</v>
+        <v>1.584556189879876</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03243683569851349</v>
+        <v>0.03171601712743541</v>
       </c>
       <c r="W46">
-        <v>0.2281513941422905</v>
+        <v>0.2283213631613507</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1297473427940539</v>
+        <v>0.1268640685097416</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5346,22 +5346,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1726458850176759</v>
+        <v>0.1745458850176759</v>
       </c>
       <c r="C47">
-        <v>-3845.98530526075</v>
+        <v>-4464.8496751373</v>
       </c>
       <c r="D47">
-        <v>14148.38469473925</v>
+        <v>13939.5863248627</v>
       </c>
       <c r="E47">
-        <v>15197.87</v>
+        <v>15607.936</v>
       </c>
       <c r="F47">
-        <v>18452.97</v>
+        <v>18863.036</v>
       </c>
       <c r="G47">
         <v>458.6</v>
@@ -5382,37 +5382,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M47">
-        <v>4351.210326</v>
+        <v>4447.9038888</v>
       </c>
       <c r="N47">
-        <v>-3799.198081102041</v>
+        <v>-3895.891643902041</v>
       </c>
       <c r="O47">
-        <v>-949.7995202755103</v>
+        <v>-973.9729109755103</v>
       </c>
       <c r="P47">
-        <v>-2849.398560826531</v>
+        <v>-2921.918732926531</v>
       </c>
       <c r="Q47">
-        <v>-2105.798560826531</v>
+        <v>-2178.318732926531</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1270932210819418</v>
+        <v>0.1285986511019778</v>
       </c>
       <c r="T47">
-        <v>1.584556189879876</v>
+        <v>1.6138998230258</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03171601712743541</v>
+        <v>0.03102653849423029</v>
       </c>
       <c r="W47">
-        <v>0.2283213631613507</v>
+        <v>0.2284839422230605</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1268640685097416</v>
+        <v>0.1241061539769212</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5428,22 +5428,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1745458850176759</v>
+        <v>0.1764458850176759</v>
       </c>
       <c r="C48">
-        <v>-4464.8496751373</v>
+        <v>-5077.640881627007</v>
       </c>
       <c r="D48">
-        <v>13939.5863248627</v>
+        <v>13736.86111837299</v>
       </c>
       <c r="E48">
-        <v>15607.936</v>
+        <v>16018.002</v>
       </c>
       <c r="F48">
-        <v>18863.036</v>
+        <v>19273.102</v>
       </c>
       <c r="G48">
         <v>458.6</v>
@@ -5464,37 +5464,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M48">
-        <v>4447.9038888</v>
+        <v>4544.5974516</v>
       </c>
       <c r="N48">
-        <v>-3895.891643902041</v>
+        <v>-3992.585206702041</v>
       </c>
       <c r="O48">
-        <v>-973.9729109755103</v>
+        <v>-998.1463016755101</v>
       </c>
       <c r="P48">
-        <v>-2921.918732926531</v>
+        <v>-2994.43890502653</v>
       </c>
       <c r="Q48">
-        <v>-2178.318732926531</v>
+        <v>-2250.83890502653</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1285986511019778</v>
+        <v>0.1301608898020151</v>
       </c>
       <c r="T48">
-        <v>1.6138998230258</v>
+        <v>1.644350763082891</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03102653849423029</v>
+        <v>0.03036639937733178</v>
       </c>
       <c r="W48">
-        <v>0.2284839422230605</v>
+        <v>0.2286396030268252</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1241061539769212</v>
+        <v>0.1214655975093271</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5510,22 +5510,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1764458850176759</v>
+        <v>0.1783458850176759</v>
       </c>
       <c r="C49">
-        <v>-5077.640881627007</v>
+        <v>-5684.620094899741</v>
       </c>
       <c r="D49">
-        <v>13736.86111837299</v>
+        <v>13539.94790510026</v>
       </c>
       <c r="E49">
-        <v>16018.002</v>
+        <v>16428.068</v>
       </c>
       <c r="F49">
-        <v>19273.102</v>
+        <v>19683.168</v>
       </c>
       <c r="G49">
         <v>458.6</v>
@@ -5546,37 +5546,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M49">
-        <v>4544.5974516</v>
+        <v>4641.291014400001</v>
       </c>
       <c r="N49">
-        <v>-3992.585206702041</v>
+        <v>-4089.278769502042</v>
       </c>
       <c r="O49">
-        <v>-998.1463016755101</v>
+        <v>-1022.31969237551</v>
       </c>
       <c r="P49">
-        <v>-2994.43890502653</v>
+        <v>-3066.959077126531</v>
       </c>
       <c r="Q49">
-        <v>-2250.83890502653</v>
+        <v>-2323.359077126531</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1301608898020151</v>
+        <v>0.1317832146059</v>
       </c>
       <c r="T49">
-        <v>1.644350763082891</v>
+        <v>1.675972893142177</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03036639937733178</v>
+        <v>0.02973376605697069</v>
       </c>
       <c r="W49">
-        <v>0.2286396030268252</v>
+        <v>0.2287887779637663</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1214655975093271</v>
+        <v>0.1189350642278827</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5592,22 +5592,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1783458850176759</v>
+        <v>0.1802458850176759</v>
       </c>
       <c r="C50">
-        <v>-5684.620094899738</v>
+        <v>-6286.033721614447</v>
       </c>
       <c r="D50">
-        <v>13539.94790510026</v>
+        <v>13348.60027838555</v>
       </c>
       <c r="E50">
-        <v>16428.068</v>
+        <v>16838.134</v>
       </c>
       <c r="F50">
-        <v>19683.168</v>
+        <v>20093.234</v>
       </c>
       <c r="G50">
         <v>458.6</v>
@@ -5628,37 +5628,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M50">
-        <v>4641.2910144</v>
+        <v>4737.9845772</v>
       </c>
       <c r="N50">
-        <v>-4089.278769502041</v>
+        <v>-4185.972332302041</v>
       </c>
       <c r="O50">
-        <v>-1022.31969237551</v>
+        <v>-1046.49308307551</v>
       </c>
       <c r="P50">
-        <v>-3066.95907712653</v>
+        <v>-3139.479249226531</v>
       </c>
       <c r="Q50">
-        <v>-2323.35907712653</v>
+        <v>-2395.879249226531</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1317832146059</v>
+        <v>0.1334691599903294</v>
       </c>
       <c r="T50">
-        <v>1.675972893142177</v>
+        <v>1.7088351067332</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.0297337660569707</v>
+        <v>0.02912695450478762</v>
       </c>
       <c r="W50">
-        <v>0.2287887779637663</v>
+        <v>0.2289318641277711</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1189350642278828</v>
+        <v>0.1165078180191504</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5674,22 +5674,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1802458850176759</v>
+        <v>0.1821458850176759</v>
       </c>
       <c r="C51">
-        <v>-6286.033721614447</v>
+        <v>-6882.114433577661</v>
       </c>
       <c r="D51">
-        <v>13348.60027838555</v>
+        <v>13162.58556642234</v>
       </c>
       <c r="E51">
-        <v>16838.134</v>
+        <v>17248.2</v>
       </c>
       <c r="F51">
-        <v>20093.234</v>
+        <v>20503.3</v>
       </c>
       <c r="G51">
         <v>458.6</v>
@@ -5710,37 +5710,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M51">
-        <v>4737.9845772</v>
+        <v>4834.67814</v>
       </c>
       <c r="N51">
-        <v>-4185.972332302041</v>
+        <v>-4282.665895102041</v>
       </c>
       <c r="O51">
-        <v>-1046.49308307551</v>
+        <v>-1070.66647377551</v>
       </c>
       <c r="P51">
-        <v>-3139.479249226531</v>
+        <v>-3211.999421326531</v>
       </c>
       <c r="Q51">
-        <v>-2395.879249226531</v>
+        <v>-2468.399421326531</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1334691599903294</v>
+        <v>0.135222543190136</v>
       </c>
       <c r="T51">
-        <v>1.7088351067332</v>
+        <v>1.743011808867864</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02912695450478762</v>
+        <v>0.02854441541469187</v>
       </c>
       <c r="W51">
-        <v>0.2289318641277711</v>
+        <v>0.2290692268452157</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1165078180191504</v>
+        <v>0.1141776616587674</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5756,22 +5756,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1821458850176759</v>
+        <v>0.1840458850176759</v>
       </c>
       <c r="C52">
-        <v>-6882.114433577661</v>
+        <v>-7473.082111577009</v>
       </c>
       <c r="D52">
-        <v>13162.58556642234</v>
+        <v>12981.68388842299</v>
       </c>
       <c r="E52">
-        <v>17248.2</v>
+        <v>17658.266</v>
       </c>
       <c r="F52">
-        <v>20503.3</v>
+        <v>20913.366</v>
       </c>
       <c r="G52">
         <v>458.6</v>
@@ -5792,37 +5792,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M52">
-        <v>4834.67814</v>
+        <v>4931.3717028</v>
       </c>
       <c r="N52">
-        <v>-4282.665895102041</v>
+        <v>-4379.359457902041</v>
       </c>
       <c r="O52">
-        <v>-1070.66647377551</v>
+        <v>-1094.83986447551</v>
       </c>
       <c r="P52">
-        <v>-3211.999421326531</v>
+        <v>-3284.519593426531</v>
       </c>
       <c r="Q52">
-        <v>-2468.399421326531</v>
+        <v>-2540.919593426531</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.135222543190136</v>
+        <v>0.1370474930511592</v>
       </c>
       <c r="T52">
-        <v>1.743011808867864</v>
+        <v>1.778583478436596</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02854441541469187</v>
+        <v>0.02798472099479595</v>
       </c>
       <c r="W52">
-        <v>0.2290692268452157</v>
+        <v>0.2292012027894271</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1141776616587674</v>
+        <v>0.1119388839791837</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5838,22 +5838,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1840458850176759</v>
+        <v>0.1859458850176759</v>
       </c>
       <c r="C53">
-        <v>-7473.082111577009</v>
+        <v>-8059.144712439693</v>
       </c>
       <c r="D53">
-        <v>12981.68388842299</v>
+        <v>12805.68728756031</v>
       </c>
       <c r="E53">
-        <v>17658.266</v>
+        <v>18068.332</v>
       </c>
       <c r="F53">
-        <v>20913.366</v>
+        <v>21323.432</v>
       </c>
       <c r="G53">
         <v>458.6</v>
@@ -5874,37 +5874,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M53">
-        <v>4931.3717028</v>
+        <v>5028.0652656</v>
       </c>
       <c r="N53">
-        <v>-4379.359457902041</v>
+        <v>-4476.053020702041</v>
       </c>
       <c r="O53">
-        <v>-1094.83986447551</v>
+        <v>-1119.01325517551</v>
       </c>
       <c r="P53">
-        <v>-3284.519593426531</v>
+        <v>-3357.039765526531</v>
       </c>
       <c r="Q53">
-        <v>-2540.919593426531</v>
+        <v>-2613.439765526531</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1370474930511592</v>
+        <v>0.1389484824897251</v>
       </c>
       <c r="T53">
-        <v>1.778583478436596</v>
+        <v>1.815637300904025</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02798472099479595</v>
+        <v>0.02744655328335757</v>
       </c>
       <c r="W53">
-        <v>0.2292012027894271</v>
+        <v>0.2293281027357843</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1119388839791837</v>
+        <v>0.1097862131334303</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5920,22 +5920,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1859458850176759</v>
+        <v>0.1878458850176759</v>
       </c>
       <c r="C54">
-        <v>-8059.144712439693</v>
+        <v>-8640.499066504555</v>
       </c>
       <c r="D54">
-        <v>12805.68728756031</v>
+        <v>12634.39893349544</v>
       </c>
       <c r="E54">
-        <v>18068.332</v>
+        <v>18478.398</v>
       </c>
       <c r="F54">
-        <v>21323.432</v>
+        <v>21733.498</v>
       </c>
       <c r="G54">
         <v>458.6</v>
@@ -5956,37 +5956,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M54">
-        <v>5028.0652656</v>
+        <v>5124.7588284</v>
       </c>
       <c r="N54">
-        <v>-4476.053020702041</v>
+        <v>-4572.746583502041</v>
       </c>
       <c r="O54">
-        <v>-1119.01325517551</v>
+        <v>-1143.18664587551</v>
       </c>
       <c r="P54">
-        <v>-3357.039765526531</v>
+        <v>-3429.559937626531</v>
       </c>
       <c r="Q54">
-        <v>-2613.439765526531</v>
+        <v>-2685.959937626531</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1389484824897251</v>
+        <v>0.1409303650958894</v>
       </c>
       <c r="T54">
-        <v>1.815637300904025</v>
+        <v>1.854267881774323</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02744655328335757</v>
+        <v>0.02692869378744516</v>
       </c>
       <c r="W54">
-        <v>0.2293281027357843</v>
+        <v>0.2294502140049204</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1097862131334303</v>
+        <v>0.1077147751497806</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6002,22 +6002,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1878458850176759</v>
+        <v>0.1897458850176759</v>
       </c>
       <c r="C55">
-        <v>-8640.499066504555</v>
+        <v>-9217.331611937198</v>
       </c>
       <c r="D55">
-        <v>12634.39893349544</v>
+        <v>12467.6323880628</v>
       </c>
       <c r="E55">
-        <v>18478.398</v>
+        <v>18888.464</v>
       </c>
       <c r="F55">
-        <v>21733.498</v>
+        <v>22143.564</v>
       </c>
       <c r="G55">
         <v>458.6</v>
@@ -6038,37 +6038,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M55">
-        <v>5124.7588284</v>
+        <v>5221.4523912</v>
       </c>
       <c r="N55">
-        <v>-4572.746583502041</v>
+        <v>-4669.440146302041</v>
       </c>
       <c r="O55">
-        <v>-1143.18664587551</v>
+        <v>-1167.36003657551</v>
       </c>
       <c r="P55">
-        <v>-3429.559937626531</v>
+        <v>-3502.080109726531</v>
       </c>
       <c r="Q55">
-        <v>-2685.959937626531</v>
+        <v>-2758.480109726531</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1409303650958894</v>
+        <v>0.1429984165110174</v>
       </c>
       <c r="T55">
-        <v>1.854267881774323</v>
+        <v>1.894578053117243</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02692869378744516</v>
+        <v>0.02643001427286284</v>
       </c>
       <c r="W55">
-        <v>0.2294502140049204</v>
+        <v>0.2295678026344589</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1077147751497806</v>
+        <v>0.1057200570914514</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6084,22 +6084,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1897458850176759</v>
+        <v>0.1916458850176759</v>
       </c>
       <c r="C56">
-        <v>-9217.331611937198</v>
+        <v>-9789.819071647551</v>
       </c>
       <c r="D56">
-        <v>12467.6323880628</v>
+        <v>12305.21092835245</v>
       </c>
       <c r="E56">
-        <v>18888.464</v>
+        <v>19298.53</v>
       </c>
       <c r="F56">
-        <v>22143.564</v>
+        <v>22553.63</v>
       </c>
       <c r="G56">
         <v>458.6</v>
@@ -6120,37 +6120,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M56">
-        <v>5221.4523912</v>
+        <v>5318.145954000001</v>
       </c>
       <c r="N56">
-        <v>-4669.440146302041</v>
+        <v>-4766.133709102041</v>
       </c>
       <c r="O56">
-        <v>-1167.36003657551</v>
+        <v>-1191.53342727551</v>
       </c>
       <c r="P56">
-        <v>-3502.080109726531</v>
+        <v>-3574.600281826531</v>
       </c>
       <c r="Q56">
-        <v>-2758.480109726531</v>
+        <v>-2831.000281826531</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1429984165110174</v>
+        <v>0.1451583813223734</v>
       </c>
       <c r="T56">
-        <v>1.894578053117243</v>
+        <v>1.93667978763096</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02643001427286284</v>
+        <v>0.02594946855881079</v>
       </c>
       <c r="W56">
-        <v>0.2295678026344589</v>
+        <v>0.2296811153138324</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1057200570914514</v>
+        <v>0.1037978742352431</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6166,22 +6166,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1916458850176759</v>
+        <v>0.1935458850176759</v>
       </c>
       <c r="C57">
-        <v>-9789.819071647551</v>
+        <v>-10358.12907797688</v>
       </c>
       <c r="D57">
-        <v>12305.21092835245</v>
+        <v>12146.96692202312</v>
       </c>
       <c r="E57">
-        <v>19298.53</v>
+        <v>19708.596</v>
       </c>
       <c r="F57">
-        <v>22553.63</v>
+        <v>22963.696</v>
       </c>
       <c r="G57">
         <v>458.6</v>
@@ -6202,37 +6202,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M57">
-        <v>5318.145954000001</v>
+        <v>5414.839516800001</v>
       </c>
       <c r="N57">
-        <v>-4766.133709102041</v>
+        <v>-4862.827271902042</v>
       </c>
       <c r="O57">
-        <v>-1191.53342727551</v>
+        <v>-1215.70681797551</v>
       </c>
       <c r="P57">
-        <v>-3574.600281826531</v>
+        <v>-3647.120453926531</v>
       </c>
       <c r="Q57">
-        <v>-2831.000281826531</v>
+        <v>-2903.520453926531</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1451583813223734</v>
+        <v>0.1474165263524273</v>
       </c>
       <c r="T57">
-        <v>1.93667978763096</v>
+        <v>1.980695237349846</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02594946855881079</v>
+        <v>0.02548608519168917</v>
       </c>
       <c r="W57">
-        <v>0.2296811153138324</v>
+        <v>0.2297903811117997</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1037978742352431</v>
+        <v>0.1019443407667566</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6248,22 +6248,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1935458850176759</v>
+        <v>0.1954458850176758</v>
       </c>
       <c r="C58">
-        <v>-10358.12907797688</v>
+        <v>-10922.42074979617</v>
       </c>
       <c r="D58">
-        <v>12146.96692202312</v>
+        <v>11992.74125020383</v>
       </c>
       <c r="E58">
-        <v>19708.596</v>
+        <v>20118.662</v>
       </c>
       <c r="F58">
-        <v>22963.696</v>
+        <v>23373.762</v>
       </c>
       <c r="G58">
         <v>458.6</v>
@@ -6284,37 +6284,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M58">
-        <v>5414.839516800001</v>
+        <v>5511.533079600001</v>
       </c>
       <c r="N58">
-        <v>-4862.827271902042</v>
+        <v>-4959.520834702042</v>
       </c>
       <c r="O58">
-        <v>-1215.70681797551</v>
+        <v>-1239.88020867551</v>
       </c>
       <c r="P58">
-        <v>-3647.120453926531</v>
+        <v>-3719.640626026531</v>
       </c>
       <c r="Q58">
-        <v>-2903.520453926531</v>
+        <v>-2976.040626026531</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1474165263524273</v>
+        <v>0.1497797013838791</v>
       </c>
       <c r="T58">
-        <v>1.980695237349846</v>
+        <v>2.026757917288214</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02548608519168917</v>
+        <v>0.02503896089008058</v>
       </c>
       <c r="W58">
-        <v>0.2297903811117997</v>
+        <v>0.229895813022119</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1019443407667566</v>
+        <v>0.1001558435603224</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6330,22 +6330,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1954458850176758</v>
+        <v>0.1973458850176759</v>
       </c>
       <c r="C59">
-        <v>-10922.42074979617</v>
+        <v>-11482.84522619248</v>
       </c>
       <c r="D59">
-        <v>11992.74125020383</v>
+        <v>11842.38277380752</v>
       </c>
       <c r="E59">
-        <v>20118.662</v>
+        <v>20528.728</v>
       </c>
       <c r="F59">
-        <v>23373.762</v>
+        <v>23783.828</v>
       </c>
       <c r="G59">
         <v>458.6</v>
@@ -6366,37 +6366,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M59">
-        <v>5511.533079600001</v>
+        <v>5608.226642400001</v>
       </c>
       <c r="N59">
-        <v>-4959.520834702042</v>
+        <v>-5056.214397502042</v>
       </c>
       <c r="O59">
-        <v>-1239.88020867551</v>
+        <v>-1264.05359937551</v>
       </c>
       <c r="P59">
-        <v>-3719.640626026531</v>
+        <v>-3792.160798126532</v>
       </c>
       <c r="Q59">
-        <v>-2976.040626026531</v>
+        <v>-3048.560798126532</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1497797013838791</v>
+        <v>0.1522554085596858</v>
       </c>
       <c r="T59">
-        <v>2.026757917288214</v>
+        <v>2.075014058176029</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02503896089008058</v>
+        <v>0.02460725466783781</v>
       </c>
       <c r="W59">
-        <v>0.229895813022119</v>
+        <v>0.2299976093493238</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1001558435603224</v>
+        <v>0.09842901867135123</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6412,22 +6412,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1973458850176758</v>
+        <v>0.1992458850176759</v>
       </c>
       <c r="C60">
-        <v>-11482.84522619247</v>
+        <v>-12039.54616050591</v>
       </c>
       <c r="D60">
-        <v>11842.38277380753</v>
+        <v>11695.74783949408</v>
       </c>
       <c r="E60">
-        <v>20528.728</v>
+        <v>20938.794</v>
       </c>
       <c r="F60">
-        <v>23783.828</v>
+        <v>24193.894</v>
       </c>
       <c r="G60">
         <v>458.6</v>
@@ -6448,37 +6448,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M60">
-        <v>5608.2266424</v>
+        <v>5704.920205199999</v>
       </c>
       <c r="N60">
-        <v>-5056.214397502041</v>
+        <v>-5152.90796030204</v>
       </c>
       <c r="O60">
-        <v>-1264.05359937551</v>
+        <v>-1288.22699007551</v>
       </c>
       <c r="P60">
-        <v>-3792.160798126531</v>
+        <v>-3864.68097022653</v>
       </c>
       <c r="Q60">
-        <v>-3048.560798126531</v>
+        <v>-3121.08097022653</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1522554085596858</v>
+        <v>0.1548518819391903</v>
       </c>
       <c r="T60">
-        <v>2.075014058176028</v>
+        <v>2.125624157155932</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02460725466783782</v>
+        <v>0.02419018255482362</v>
       </c>
       <c r="W60">
-        <v>0.2299976093493238</v>
+        <v>0.2300959549535726</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.09842901867135123</v>
+        <v>0.09676073021929443</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6494,22 +6494,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1992458850176759</v>
+        <v>0.2011458850176758</v>
       </c>
       <c r="C61">
-        <v>-12039.54616050591</v>
+        <v>-12592.66017811198</v>
       </c>
       <c r="D61">
-        <v>11695.74783949408</v>
+        <v>11552.69982188802</v>
       </c>
       <c r="E61">
-        <v>20938.794</v>
+        <v>21348.86</v>
       </c>
       <c r="F61">
-        <v>24193.894</v>
+        <v>24603.96</v>
       </c>
       <c r="G61">
         <v>458.6</v>
@@ -6530,37 +6530,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M61">
-        <v>5704.920205199999</v>
+        <v>5801.613768</v>
       </c>
       <c r="N61">
-        <v>-5152.90796030204</v>
+        <v>-5249.601523102041</v>
       </c>
       <c r="O61">
-        <v>-1288.22699007551</v>
+        <v>-1312.40038077551</v>
       </c>
       <c r="P61">
-        <v>-3864.68097022653</v>
+        <v>-3937.201142326531</v>
       </c>
       <c r="Q61">
-        <v>-3121.08097022653</v>
+        <v>-3193.601142326531</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1548518819391903</v>
+        <v>0.15757817898767</v>
       </c>
       <c r="T61">
-        <v>2.125624157155932</v>
+        <v>2.17876476108483</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02419018255482362</v>
+        <v>0.02378701284557656</v>
       </c>
       <c r="W61">
-        <v>0.2300959549535726</v>
+        <v>0.230191022371013</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.09676073021929443</v>
+        <v>0.0951480513823062</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6576,22 +6576,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2011458850176758</v>
+        <v>0.2030458850176758</v>
       </c>
       <c r="C62">
-        <v>-12592.66017811198</v>
+        <v>-13142.31730101558</v>
       </c>
       <c r="D62">
-        <v>11552.69982188802</v>
+        <v>11413.10869898442</v>
       </c>
       <c r="E62">
-        <v>21348.86</v>
+        <v>21758.926</v>
       </c>
       <c r="F62">
-        <v>24603.96</v>
+        <v>25014.026</v>
       </c>
       <c r="G62">
         <v>458.6</v>
@@ -6612,37 +6612,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M62">
-        <v>5801.613768</v>
+        <v>5898.307330799999</v>
       </c>
       <c r="N62">
-        <v>-5249.601523102041</v>
+        <v>-5346.29508590204</v>
       </c>
       <c r="O62">
-        <v>-1312.40038077551</v>
+        <v>-1336.57377147551</v>
       </c>
       <c r="P62">
-        <v>-3937.201142326531</v>
+        <v>-4009.72131442653</v>
       </c>
       <c r="Q62">
-        <v>-3193.601142326531</v>
+        <v>-3266.12131442653</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.15757817898767</v>
+        <v>0.1604442861412</v>
       </c>
       <c r="T62">
-        <v>2.17876476108483</v>
+        <v>2.234630524189569</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02378701284557656</v>
+        <v>0.02339706181532121</v>
       </c>
       <c r="W62">
-        <v>0.230191022371013</v>
+        <v>0.2302829728239473</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.0951480513823062</v>
+        <v>0.09358824726128478</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6658,22 +6658,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2030458850176758</v>
+        <v>0.2049458850176759</v>
       </c>
       <c r="C63">
-        <v>-13142.31730101558</v>
+        <v>-13688.64134203035</v>
       </c>
       <c r="D63">
-        <v>11413.10869898442</v>
+        <v>11276.85065796965</v>
       </c>
       <c r="E63">
-        <v>21758.926</v>
+        <v>22168.992</v>
       </c>
       <c r="F63">
-        <v>25014.026</v>
+        <v>25424.092</v>
       </c>
       <c r="G63">
         <v>458.6</v>
@@ -6694,37 +6694,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M63">
-        <v>5898.307330799999</v>
+        <v>5995.0008936</v>
       </c>
       <c r="N63">
-        <v>-5346.29508590204</v>
+        <v>-5442.988648702041</v>
       </c>
       <c r="O63">
-        <v>-1336.57377147551</v>
+        <v>-1360.74716217551</v>
       </c>
       <c r="P63">
-        <v>-4009.72131442653</v>
+        <v>-4082.241486526531</v>
       </c>
       <c r="Q63">
-        <v>-3266.12131442653</v>
+        <v>-3338.641486526531</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1604442861412</v>
+        <v>0.1634612410396527</v>
       </c>
       <c r="T63">
-        <v>2.234630524189569</v>
+        <v>2.29343659061561</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02339706181532121</v>
+        <v>0.02301968985055796</v>
       </c>
       <c r="W63">
-        <v>0.2302829728239473</v>
+        <v>0.2303719571332385</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.09358824726128478</v>
+        <v>0.09207875940223176</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6740,22 +6740,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2049458850176759</v>
+        <v>0.2068458850176758</v>
       </c>
       <c r="C64">
-        <v>-13688.64134203035</v>
+        <v>-14231.75027105514</v>
       </c>
       <c r="D64">
-        <v>11276.85065796965</v>
+        <v>11143.80772894486</v>
       </c>
       <c r="E64">
-        <v>22168.992</v>
+        <v>22579.058</v>
       </c>
       <c r="F64">
-        <v>25424.092</v>
+        <v>25834.158</v>
       </c>
       <c r="G64">
         <v>458.6</v>
@@ -6776,37 +6776,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M64">
-        <v>5995.0008936</v>
+        <v>6091.6944564</v>
       </c>
       <c r="N64">
-        <v>-5442.988648702041</v>
+        <v>-5539.682211502041</v>
       </c>
       <c r="O64">
-        <v>-1360.74716217551</v>
+        <v>-1384.92055287551</v>
       </c>
       <c r="P64">
-        <v>-4082.241486526531</v>
+        <v>-4154.761658626531</v>
       </c>
       <c r="Q64">
-        <v>-3338.641486526531</v>
+        <v>-3411.161658626531</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1634612410396527</v>
+        <v>0.1666412745812649</v>
       </c>
       <c r="T64">
-        <v>2.29343659061561</v>
+        <v>2.355421363334951</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02301968985055796</v>
+        <v>0.02265429794816815</v>
       </c>
       <c r="W64">
-        <v>0.2303719571332385</v>
+        <v>0.230458116543822</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.09207875940223176</v>
+        <v>0.09061719179267258</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6822,22 +6822,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2068458850176758</v>
+        <v>0.2087458850176759</v>
       </c>
       <c r="C65">
-        <v>-14231.75027105514</v>
+        <v>-14771.75655572511</v>
       </c>
       <c r="D65">
-        <v>11143.80772894486</v>
+        <v>11013.86744427489</v>
       </c>
       <c r="E65">
-        <v>22579.058</v>
+        <v>22989.124</v>
       </c>
       <c r="F65">
-        <v>25834.158</v>
+        <v>26244.224</v>
       </c>
       <c r="G65">
         <v>458.6</v>
@@ -6858,37 +6858,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M65">
-        <v>6091.6944564</v>
+        <v>6188.3880192</v>
       </c>
       <c r="N65">
-        <v>-5539.682211502041</v>
+        <v>-5636.375774302041</v>
       </c>
       <c r="O65">
-        <v>-1384.92055287551</v>
+        <v>-1409.09394357551</v>
       </c>
       <c r="P65">
-        <v>-4154.761658626531</v>
+        <v>-4227.281830726531</v>
       </c>
       <c r="Q65">
-        <v>-3411.161658626531</v>
+        <v>-3483.681830726531</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1666412745812649</v>
+        <v>0.1699979766529667</v>
       </c>
       <c r="T65">
-        <v>2.355421363334951</v>
+        <v>2.4208497345387</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02265429794816815</v>
+        <v>0.02230032454272802</v>
       </c>
       <c r="W65">
-        <v>0.230458116543822</v>
+        <v>0.2305415834728247</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.09061719179267258</v>
+        <v>0.08920129817091205</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6904,22 +6904,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2087458850176759</v>
+        <v>0.2106458850176758</v>
       </c>
       <c r="C66">
-        <v>-14771.75655572511</v>
+        <v>-15308.76747850482</v>
       </c>
       <c r="D66">
-        <v>11013.86744427489</v>
+        <v>10886.92252149518</v>
       </c>
       <c r="E66">
-        <v>22989.124</v>
+        <v>23399.19</v>
       </c>
       <c r="F66">
-        <v>26244.224</v>
+        <v>26654.29</v>
       </c>
       <c r="G66">
         <v>458.6</v>
@@ -6940,37 +6940,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M66">
-        <v>6188.3880192</v>
+        <v>6285.081582000001</v>
       </c>
       <c r="N66">
-        <v>-5636.375774302041</v>
+        <v>-5733.069337102042</v>
       </c>
       <c r="O66">
-        <v>-1409.09394357551</v>
+        <v>-1433.26733427551</v>
       </c>
       <c r="P66">
-        <v>-4227.281830726531</v>
+        <v>-4299.802002826531</v>
       </c>
       <c r="Q66">
-        <v>-3483.681830726531</v>
+        <v>-3556.202002826531</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1699979766529667</v>
+        <v>0.1735464902716229</v>
       </c>
       <c r="T66">
-        <v>2.4208497345387</v>
+        <v>2.490016869811234</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02230032454272802</v>
+        <v>0.02195724262668605</v>
       </c>
       <c r="W66">
-        <v>0.2305415834728247</v>
+        <v>0.2306224821886274</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.08920129817091205</v>
+        <v>0.08782897050674421</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6986,22 +6986,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2106458850176758</v>
+        <v>0.2125458850176759</v>
       </c>
       <c r="C67">
-        <v>-15308.76747850482</v>
+        <v>-15842.88543210264</v>
       </c>
       <c r="D67">
-        <v>10886.92252149518</v>
+        <v>10762.87056789736</v>
       </c>
       <c r="E67">
-        <v>23399.19</v>
+        <v>23809.256</v>
       </c>
       <c r="F67">
-        <v>26654.29</v>
+        <v>27064.356</v>
       </c>
       <c r="G67">
         <v>458.6</v>
@@ -7022,37 +7022,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M67">
-        <v>6285.081582000001</v>
+        <v>6381.7751448</v>
       </c>
       <c r="N67">
-        <v>-5733.069337102042</v>
+        <v>-5829.762899902041</v>
       </c>
       <c r="O67">
-        <v>-1433.26733427551</v>
+        <v>-1457.44072497551</v>
       </c>
       <c r="P67">
-        <v>-4299.802002826531</v>
+        <v>-4372.32217492653</v>
       </c>
       <c r="Q67">
-        <v>-3556.202002826531</v>
+        <v>-3628.72217492653</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1735464902716229</v>
+        <v>0.1773037399854942</v>
       </c>
       <c r="T67">
-        <v>2.490016869811234</v>
+        <v>2.5632526600998</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02195724262668605</v>
+        <v>0.02162455713234232</v>
       </c>
       <c r="W67">
-        <v>0.2306224821886274</v>
+        <v>0.2307009294281937</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.08782897050674421</v>
+        <v>0.08649822852936928</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7068,22 +7068,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2125458850176759</v>
+        <v>0.2144458850176759</v>
       </c>
       <c r="C68">
-        <v>-15842.88543210264</v>
+        <v>-16374.20819491581</v>
       </c>
       <c r="D68">
-        <v>10762.87056789736</v>
+        <v>10641.61380508419</v>
       </c>
       <c r="E68">
-        <v>23809.256</v>
+        <v>24219.322</v>
       </c>
       <c r="F68">
-        <v>27064.356</v>
+        <v>27474.422</v>
       </c>
       <c r="G68">
         <v>458.6</v>
@@ -7104,37 +7104,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M68">
-        <v>6381.7751448</v>
+        <v>6478.468707600001</v>
       </c>
       <c r="N68">
-        <v>-5829.762899902041</v>
+        <v>-5926.456462702042</v>
       </c>
       <c r="O68">
-        <v>-1457.44072497551</v>
+        <v>-1481.61411567551</v>
       </c>
       <c r="P68">
-        <v>-4372.32217492653</v>
+        <v>-4444.842347026532</v>
       </c>
       <c r="Q68">
-        <v>-3628.72217492653</v>
+        <v>-3701.242347026532</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1773037399854942</v>
+        <v>0.1812887018032364</v>
       </c>
       <c r="T68">
-        <v>2.5632526600998</v>
+        <v>2.640926983133128</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02162455713234232</v>
+        <v>0.02130180254827751</v>
       </c>
       <c r="W68">
-        <v>0.2307009294281937</v>
+        <v>0.2307770349591162</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.08649822852936928</v>
+        <v>0.08520721019311006</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7150,22 +7150,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2144458850176759</v>
+        <v>0.2163458850176758</v>
       </c>
       <c r="C69">
-        <v>-16374.20819491581</v>
+        <v>-16902.82918806364</v>
       </c>
       <c r="D69">
-        <v>10641.61380508419</v>
+        <v>10523.05881193636</v>
       </c>
       <c r="E69">
-        <v>24219.322</v>
+        <v>24629.388</v>
       </c>
       <c r="F69">
-        <v>27474.422</v>
+        <v>27884.488</v>
       </c>
       <c r="G69">
         <v>458.6</v>
@@ -7186,37 +7186,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M69">
-        <v>6478.468707600001</v>
+        <v>6575.1622704</v>
       </c>
       <c r="N69">
-        <v>-5926.456462702042</v>
+        <v>-6023.150025502041</v>
       </c>
       <c r="O69">
-        <v>-1481.61411567551</v>
+        <v>-1505.78750637551</v>
       </c>
       <c r="P69">
-        <v>-4444.842347026532</v>
+        <v>-4517.362519126531</v>
       </c>
       <c r="Q69">
-        <v>-3701.242347026532</v>
+        <v>-3773.762519126531</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1812887018032364</v>
+        <v>0.1855227237345876</v>
       </c>
       <c r="T69">
-        <v>2.640926983133128</v>
+        <v>2.723455951356038</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02130180254827751</v>
+        <v>0.02098854074609696</v>
       </c>
       <c r="W69">
-        <v>0.2307770349591162</v>
+        <v>0.2308509020920703</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.08520721019311006</v>
+        <v>0.08395416298438785</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7232,22 +7232,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2163458850176758</v>
+        <v>0.2182458850176759</v>
       </c>
       <c r="C70">
-        <v>-16902.82918806364</v>
+        <v>-17428.83771542885</v>
       </c>
       <c r="D70">
-        <v>10523.05881193636</v>
+        <v>10407.11628457116</v>
       </c>
       <c r="E70">
-        <v>24629.388</v>
+        <v>25039.454</v>
       </c>
       <c r="F70">
-        <v>27884.488</v>
+        <v>28294.554</v>
       </c>
       <c r="G70">
         <v>458.6</v>
@@ -7268,37 +7268,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M70">
-        <v>6575.1622704</v>
+        <v>6671.8558332</v>
       </c>
       <c r="N70">
-        <v>-6023.150025502041</v>
+        <v>-6119.843588302041</v>
       </c>
       <c r="O70">
-        <v>-1505.78750637551</v>
+        <v>-1529.96089707551</v>
       </c>
       <c r="P70">
-        <v>-4517.362519126531</v>
+        <v>-4589.88269122653</v>
       </c>
       <c r="Q70">
-        <v>-3773.762519126531</v>
+        <v>-3846.28269122653</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1855227237345876</v>
+        <v>0.1900299083711872</v>
       </c>
       <c r="T70">
-        <v>2.723455951356038</v>
+        <v>2.811309369141717</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02098854074609696</v>
+        <v>0.02068435899615353</v>
       </c>
       <c r="W70">
-        <v>0.2308509020920703</v>
+        <v>0.230922628148707</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.08395416298438785</v>
+        <v>0.08273743598461414</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7314,22 +7314,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2182458850176759</v>
+        <v>0.2201458850176759</v>
       </c>
       <c r="C71">
-        <v>-17428.83771542885</v>
+        <v>-17952.31918800326</v>
       </c>
       <c r="D71">
-        <v>10407.11628457116</v>
+        <v>10293.70081199674</v>
       </c>
       <c r="E71">
-        <v>25039.454</v>
+        <v>25449.52</v>
       </c>
       <c r="F71">
-        <v>28294.554</v>
+        <v>28704.62</v>
       </c>
       <c r="G71">
         <v>458.6</v>
@@ -7350,37 +7350,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M71">
-        <v>6671.8558332</v>
+        <v>6768.549396000001</v>
       </c>
       <c r="N71">
-        <v>-6119.843588302041</v>
+        <v>-6216.537151102042</v>
       </c>
       <c r="O71">
-        <v>-1529.96089707551</v>
+        <v>-1554.134287775511</v>
       </c>
       <c r="P71">
-        <v>-4589.88269122653</v>
+        <v>-4662.402863326532</v>
       </c>
       <c r="Q71">
-        <v>-3846.28269122653</v>
+        <v>-3918.802863326532</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1900299083711872</v>
+        <v>0.1948375719835601</v>
       </c>
       <c r="T71">
-        <v>2.811309369141717</v>
+        <v>2.90501968144644</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02068435899615353</v>
+        <v>0.02038886815335133</v>
       </c>
       <c r="W71">
-        <v>0.230922628148707</v>
+        <v>0.2309923048894398</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.08273743598461414</v>
+        <v>0.08155547261340534</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7396,22 +7396,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2201458850176759</v>
+        <v>0.2220458850176759</v>
       </c>
       <c r="C72">
-        <v>-17952.31918800326</v>
+        <v>-18473.3553337223</v>
       </c>
       <c r="D72">
-        <v>10293.70081199674</v>
+        <v>10182.7306662777</v>
       </c>
       <c r="E72">
-        <v>25449.52</v>
+        <v>25859.586</v>
       </c>
       <c r="F72">
-        <v>28704.62</v>
+        <v>29114.686</v>
       </c>
       <c r="G72">
         <v>458.6</v>
@@ -7432,37 +7432,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M72">
-        <v>6768.549396000001</v>
+        <v>6865.2429588</v>
       </c>
       <c r="N72">
-        <v>-6216.537151102042</v>
+        <v>-6313.230713902041</v>
       </c>
       <c r="O72">
-        <v>-1554.134287775511</v>
+        <v>-1578.30767847551</v>
       </c>
       <c r="P72">
-        <v>-4662.402863326532</v>
+        <v>-4734.923035426531</v>
       </c>
       <c r="Q72">
-        <v>-3918.802863326532</v>
+        <v>-3991.323035426531</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1948375719835601</v>
+        <v>0.1999767986036829</v>
       </c>
       <c r="T72">
-        <v>2.90501968144644</v>
+        <v>3.005192773910111</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02038886815335133</v>
+        <v>0.02010170099626188</v>
       </c>
       <c r="W72">
-        <v>0.2309923048894398</v>
+        <v>0.2310600189050815</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.08155547261340534</v>
+        <v>0.08040680398504751</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7478,22 +7478,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2220458850176759</v>
+        <v>0.2239458850176758</v>
       </c>
       <c r="C73">
-        <v>-18473.3553337223</v>
+        <v>-18992.02439387162</v>
       </c>
       <c r="D73">
-        <v>10182.7306662777</v>
+        <v>10074.12760612838</v>
       </c>
       <c r="E73">
-        <v>25859.586</v>
+        <v>26269.652</v>
       </c>
       <c r="F73">
-        <v>29114.686</v>
+        <v>29524.752</v>
       </c>
       <c r="G73">
         <v>458.6</v>
@@ -7514,37 +7514,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M73">
-        <v>6865.2429588</v>
+        <v>6961.9365216</v>
       </c>
       <c r="N73">
-        <v>-6313.23071390204</v>
+        <v>-6409.924276702041</v>
       </c>
       <c r="O73">
-        <v>-1578.30767847551</v>
+        <v>-1602.48106917551</v>
       </c>
       <c r="P73">
-        <v>-4734.92303542653</v>
+        <v>-4807.44320752653</v>
       </c>
       <c r="Q73">
-        <v>-3991.32303542653</v>
+        <v>-4063.84320752653</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1999767986036828</v>
+        <v>0.2054831128395286</v>
       </c>
       <c r="T73">
-        <v>3.00519277391011</v>
+        <v>3.112521087264043</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02010170099626188</v>
+        <v>0.01982251070464713</v>
       </c>
       <c r="W73">
-        <v>0.2310600189050815</v>
+        <v>0.2311258519758442</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.08040680398504751</v>
+        <v>0.07929004281858854</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7560,22 +7560,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2239458850176758</v>
+        <v>0.2258458850176758</v>
       </c>
       <c r="C74">
-        <v>-18992.02439387162</v>
+        <v>-19508.4013070578</v>
       </c>
       <c r="D74">
-        <v>10074.12760612838</v>
+        <v>9967.8166929422</v>
       </c>
       <c r="E74">
-        <v>26269.652</v>
+        <v>26679.718</v>
       </c>
       <c r="F74">
-        <v>29524.752</v>
+        <v>29934.818</v>
       </c>
       <c r="G74">
         <v>458.6</v>
@@ -7596,37 +7596,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M74">
-        <v>6961.9365216</v>
+        <v>7058.6300844</v>
       </c>
       <c r="N74">
-        <v>-6409.924276702041</v>
+        <v>-6506.617839502041</v>
       </c>
       <c r="O74">
-        <v>-1602.48106917551</v>
+        <v>-1626.65445987551</v>
       </c>
       <c r="P74">
-        <v>-4807.44320752653</v>
+        <v>-4879.963379626531</v>
       </c>
       <c r="Q74">
-        <v>-4063.84320752653</v>
+        <v>-4136.36337962653</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2054831128395286</v>
+        <v>0.2113973022039556</v>
       </c>
       <c r="T74">
-        <v>3.112521087264043</v>
+        <v>3.227799646051599</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01982251070464713</v>
+        <v>0.01955096946211772</v>
       </c>
       <c r="W74">
-        <v>0.2311258519758442</v>
+        <v>0.2311898814008326</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.07929004281858854</v>
+        <v>0.07820387784847083</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7642,22 +7642,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2258458850176758</v>
+        <v>0.2277458850176758</v>
       </c>
       <c r="C75">
-        <v>-19508.4013070578</v>
+        <v>-20022.55788165228</v>
       </c>
       <c r="D75">
-        <v>9967.8166929422</v>
+        <v>9863.72611834772</v>
       </c>
       <c r="E75">
-        <v>26679.718</v>
+        <v>27089.784</v>
       </c>
       <c r="F75">
-        <v>29934.818</v>
+        <v>30344.884</v>
       </c>
       <c r="G75">
         <v>458.6</v>
@@ -7678,37 +7678,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M75">
-        <v>7058.6300844</v>
+        <v>7155.3236472</v>
       </c>
       <c r="N75">
-        <v>-6506.617839502041</v>
+        <v>-6603.311402302041</v>
       </c>
       <c r="O75">
-        <v>-1626.65445987551</v>
+        <v>-1650.82785057551</v>
       </c>
       <c r="P75">
-        <v>-4879.963379626531</v>
+        <v>-4952.483551726531</v>
       </c>
       <c r="Q75">
-        <v>-4136.36337962653</v>
+        <v>-4208.883551726531</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2113973022039556</v>
+        <v>0.2177664292118001</v>
       </c>
       <c r="T75">
-        <v>3.227799646051599</v>
+        <v>3.351945786284353</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01955096946211772</v>
+        <v>0.0192867671720891</v>
       </c>
       <c r="W75">
-        <v>0.2311898814008326</v>
+        <v>0.2312521803008214</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.07820387784847083</v>
+        <v>0.07714706868835641</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7724,22 +7724,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2277458850176758</v>
+        <v>0.2296458850176759</v>
       </c>
       <c r="C76">
-        <v>-20022.55788165228</v>
+        <v>-20534.56295754217</v>
       </c>
       <c r="D76">
-        <v>9863.72611834772</v>
+        <v>9761.78704245783</v>
       </c>
       <c r="E76">
-        <v>27089.784</v>
+        <v>27499.85</v>
       </c>
       <c r="F76">
-        <v>30344.884</v>
+        <v>30754.95</v>
       </c>
       <c r="G76">
         <v>458.6</v>
@@ -7760,37 +7760,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M76">
-        <v>7155.3236472</v>
+        <v>7252.01721</v>
       </c>
       <c r="N76">
-        <v>-6603.311402302041</v>
+        <v>-6700.004965102041</v>
       </c>
       <c r="O76">
-        <v>-1650.82785057551</v>
+        <v>-1675.00124127551</v>
       </c>
       <c r="P76">
-        <v>-4952.483551726531</v>
+        <v>-5025.00372382653</v>
       </c>
       <c r="Q76">
-        <v>-4208.883551726531</v>
+        <v>-4281.40372382653</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2177664292118001</v>
+        <v>0.2246450863802721</v>
       </c>
       <c r="T76">
-        <v>3.351945786284353</v>
+        <v>3.486023617735728</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0192867671720891</v>
+        <v>0.01902961027646125</v>
       </c>
       <c r="W76">
-        <v>0.2312521803008214</v>
+        <v>0.2313128178968105</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.07714706868835641</v>
+        <v>0.07611844110584498</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7806,22 +7806,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2296458850176759</v>
+        <v>0.2315458850176758</v>
       </c>
       <c r="C77">
-        <v>-20534.56295754217</v>
+        <v>-21044.48255795386</v>
       </c>
       <c r="D77">
-        <v>9761.78704245783</v>
+        <v>9661.933442046142</v>
       </c>
       <c r="E77">
-        <v>27499.85</v>
+        <v>27909.916</v>
       </c>
       <c r="F77">
-        <v>30754.95</v>
+        <v>31165.016</v>
       </c>
       <c r="G77">
         <v>458.6</v>
@@ -7842,37 +7842,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M77">
-        <v>7252.01721</v>
+        <v>7348.7107728</v>
       </c>
       <c r="N77">
-        <v>-6700.004965102041</v>
+        <v>-6796.698527902041</v>
       </c>
       <c r="O77">
-        <v>-1675.00124127551</v>
+        <v>-1699.17463197551</v>
       </c>
       <c r="P77">
-        <v>-5025.00372382653</v>
+        <v>-5097.523895926531</v>
       </c>
       <c r="Q77">
-        <v>-4281.40372382653</v>
+        <v>-4353.92389592653</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2246450863802721</v>
+        <v>0.2320969649794501</v>
       </c>
       <c r="T77">
-        <v>3.486023617735728</v>
+        <v>3.63127460180805</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01902961027646125</v>
+        <v>0.01877922066756044</v>
       </c>
       <c r="W77">
-        <v>0.2313128178968105</v>
+        <v>0.2313718597665892</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.07611844110584498</v>
+        <v>0.07511688267024175</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7888,22 +7888,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2315458850176758</v>
+        <v>0.2334458850176759</v>
       </c>
       <c r="C78">
-        <v>-21044.48255795386</v>
+        <v>-21552.38003205284</v>
       </c>
       <c r="D78">
-        <v>9661.933442046142</v>
+        <v>9564.101967947159</v>
       </c>
       <c r="E78">
-        <v>27909.916</v>
+        <v>28319.982</v>
       </c>
       <c r="F78">
-        <v>31165.016</v>
+        <v>31575.082</v>
       </c>
       <c r="G78">
         <v>458.6</v>
@@ -7924,37 +7924,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M78">
-        <v>7348.7107728</v>
+        <v>7445.4043356</v>
       </c>
       <c r="N78">
-        <v>-6796.698527902041</v>
+        <v>-6893.392090702041</v>
       </c>
       <c r="O78">
-        <v>-1699.17463197551</v>
+        <v>-1723.34802267551</v>
       </c>
       <c r="P78">
-        <v>-5097.523895926531</v>
+        <v>-5170.044068026531</v>
       </c>
       <c r="Q78">
-        <v>-4353.92389592653</v>
+        <v>-4426.444068026531</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2320969649794501</v>
+        <v>0.2401968330220349</v>
       </c>
       <c r="T78">
-        <v>3.63127460180805</v>
+        <v>3.789156106234487</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01877922066756044</v>
+        <v>0.01853533468486485</v>
       </c>
       <c r="W78">
-        <v>0.2313718597665892</v>
+        <v>0.2314293680813089</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.07511688267024175</v>
+        <v>0.07414133873945938</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7970,22 +7970,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2334458850176759</v>
+        <v>0.2353458850176759</v>
       </c>
       <c r="C79">
-        <v>-21552.38003205284</v>
+        <v>-22058.31618896712</v>
       </c>
       <c r="D79">
-        <v>9564.101967947159</v>
+        <v>9468.231811032883</v>
       </c>
       <c r="E79">
-        <v>28319.982</v>
+        <v>28730.048</v>
       </c>
       <c r="F79">
-        <v>31575.082</v>
+        <v>31985.148</v>
       </c>
       <c r="G79">
         <v>458.6</v>
@@ -8006,37 +8006,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M79">
-        <v>7445.4043356</v>
+        <v>7542.0978984</v>
       </c>
       <c r="N79">
-        <v>-6893.392090702041</v>
+        <v>-6990.085653502041</v>
       </c>
       <c r="O79">
-        <v>-1723.34802267551</v>
+        <v>-1747.52141337551</v>
       </c>
       <c r="P79">
-        <v>-5170.044068026531</v>
+        <v>-5242.56424012653</v>
       </c>
       <c r="Q79">
-        <v>-4426.444068026531</v>
+        <v>-4498.96424012653</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2401968330220349</v>
+        <v>0.2490330527048547</v>
       </c>
       <c r="T79">
-        <v>3.789156106234487</v>
+        <v>3.961390474699692</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01853533468486485</v>
+        <v>0.01829770218890504</v>
       </c>
       <c r="W79">
-        <v>0.2314293680813089</v>
+        <v>0.2314854018238562</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.07414133873945938</v>
+        <v>0.07319080875562012</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8052,22 +8052,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2353458850176759</v>
+        <v>0.2372458850176759</v>
       </c>
       <c r="C80">
-        <v>-22058.31618896712</v>
+        <v>-22562.34942382987</v>
       </c>
       <c r="D80">
-        <v>9468.231811032883</v>
+        <v>9374.264576170133</v>
       </c>
       <c r="E80">
-        <v>28730.048</v>
+        <v>29140.114</v>
       </c>
       <c r="F80">
-        <v>31985.148</v>
+        <v>32395.214</v>
       </c>
       <c r="G80">
         <v>458.6</v>
@@ -8088,37 +8088,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M80">
-        <v>7542.0978984</v>
+        <v>7638.7914612</v>
       </c>
       <c r="N80">
-        <v>-6990.085653502041</v>
+        <v>-7086.779216302041</v>
       </c>
       <c r="O80">
-        <v>-1747.52141337551</v>
+        <v>-1771.69480407551</v>
       </c>
       <c r="P80">
-        <v>-5242.56424012653</v>
+        <v>-5315.084412226531</v>
       </c>
       <c r="Q80">
-        <v>-4498.96424012653</v>
+        <v>-4571.48441222653</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2490330527048547</v>
+        <v>0.2587108171193716</v>
       </c>
       <c r="T80">
-        <v>3.961390474699692</v>
+        <v>4.150028116352058</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01829770218890504</v>
+        <v>0.01806608570550118</v>
       </c>
       <c r="W80">
-        <v>0.2314854018238562</v>
+        <v>0.2315400169906428</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.07319080875562012</v>
+        <v>0.07226434282200467</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8134,22 +8134,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2372458850176759</v>
+        <v>0.2391458850176759</v>
       </c>
       <c r="C81">
-        <v>-22562.34942382987</v>
+        <v>-23064.53583639046</v>
       </c>
       <c r="D81">
-        <v>9374.264576170133</v>
+        <v>9282.144163609539</v>
       </c>
       <c r="E81">
-        <v>29140.114</v>
+        <v>29550.18</v>
       </c>
       <c r="F81">
-        <v>32395.214</v>
+        <v>32805.28</v>
       </c>
       <c r="G81">
         <v>458.6</v>
@@ -8170,37 +8170,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M81">
-        <v>7638.7914612</v>
+        <v>7735.485024</v>
       </c>
       <c r="N81">
-        <v>-7086.779216302041</v>
+        <v>-7183.47277910204</v>
       </c>
       <c r="O81">
-        <v>-1771.69480407551</v>
+        <v>-1795.86819477551</v>
       </c>
       <c r="P81">
-        <v>-5315.084412226531</v>
+        <v>-5387.60458432653</v>
       </c>
       <c r="Q81">
-        <v>-4571.48441222653</v>
+        <v>-4644.00458432653</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2587108171193716</v>
+        <v>0.2693563579753401</v>
       </c>
       <c r="T81">
-        <v>4.150028116352058</v>
+        <v>4.357529522169661</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01806608570550118</v>
+        <v>0.01784025963418242</v>
       </c>
       <c r="W81">
-        <v>0.2315400169906428</v>
+        <v>0.2315932667782598</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.07226434282200467</v>
+        <v>0.0713610385367297</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8216,22 +8216,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2391458850176759</v>
+        <v>0.2410458850176758</v>
       </c>
       <c r="C82">
-        <v>-23064.53583639046</v>
+        <v>-23564.92934270007</v>
       </c>
       <c r="D82">
-        <v>9282.144163609539</v>
+        <v>9191.816657299931</v>
       </c>
       <c r="E82">
-        <v>29550.18</v>
+        <v>29960.246</v>
       </c>
       <c r="F82">
-        <v>32805.28</v>
+        <v>33215.346</v>
       </c>
       <c r="G82">
         <v>458.6</v>
@@ -8252,37 +8252,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M82">
-        <v>7735.485024</v>
+        <v>7832.1785868</v>
       </c>
       <c r="N82">
-        <v>-7183.47277910204</v>
+        <v>-7280.166341902041</v>
       </c>
       <c r="O82">
-        <v>-1795.86819477551</v>
+        <v>-1820.04158547551</v>
       </c>
       <c r="P82">
-        <v>-5387.60458432653</v>
+        <v>-5460.12475642653</v>
       </c>
       <c r="Q82">
-        <v>-4644.00458432653</v>
+        <v>-4716.52475642653</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2693563579753401</v>
+        <v>0.2811224820793054</v>
       </c>
       <c r="T82">
-        <v>4.357529522169661</v>
+        <v>4.586873181231222</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01784025963418242</v>
+        <v>0.01762000951524189</v>
       </c>
       <c r="W82">
-        <v>0.2315932667782598</v>
+        <v>0.231645201756306</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.0713610385367297</v>
+        <v>0.07048003806096759</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8298,22 +8298,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2410458850176758</v>
+        <v>0.2429458850176759</v>
       </c>
       <c r="C83">
-        <v>-23564.92934270007</v>
+        <v>-24063.5817803389</v>
       </c>
       <c r="D83">
-        <v>9191.816657299931</v>
+        <v>9103.230219661102</v>
       </c>
       <c r="E83">
-        <v>29960.246</v>
+        <v>30370.31200000001</v>
       </c>
       <c r="F83">
-        <v>33215.346</v>
+        <v>33625.412</v>
       </c>
       <c r="G83">
         <v>458.6</v>
@@ -8334,37 +8334,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M83">
-        <v>7832.1785868</v>
+        <v>7928.872149600002</v>
       </c>
       <c r="N83">
-        <v>-7280.166341902041</v>
+        <v>-7376.859904702043</v>
       </c>
       <c r="O83">
-        <v>-1820.04158547551</v>
+        <v>-1844.214976175511</v>
       </c>
       <c r="P83">
-        <v>-5460.12475642653</v>
+        <v>-5532.644928526532</v>
       </c>
       <c r="Q83">
-        <v>-4716.52475642653</v>
+        <v>-4789.044928526531</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2811224820793054</v>
+        <v>0.2941959533059335</v>
       </c>
       <c r="T83">
-        <v>4.586873181231222</v>
+        <v>4.841699469077401</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01762000951524189</v>
+        <v>0.01740513135042187</v>
       </c>
       <c r="W83">
-        <v>0.231645201756306</v>
+        <v>0.2316958700275705</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.07048003806096759</v>
+        <v>0.06962052540168751</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8380,22 +8380,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2429458850176759</v>
+        <v>0.2448458850176759</v>
       </c>
       <c r="C84">
-        <v>-24063.5817803389</v>
+        <v>-24560.54300761687</v>
       </c>
       <c r="D84">
-        <v>9103.230219661102</v>
+        <v>9016.33499238313</v>
       </c>
       <c r="E84">
-        <v>30370.31200000001</v>
+        <v>30780.378</v>
       </c>
       <c r="F84">
-        <v>33625.412</v>
+        <v>34035.478</v>
       </c>
       <c r="G84">
         <v>458.6</v>
@@ -8416,37 +8416,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M84">
-        <v>7928.872149600002</v>
+        <v>8025.565712400001</v>
       </c>
       <c r="N84">
-        <v>-7376.859904702043</v>
+        <v>-7473.553467502042</v>
       </c>
       <c r="O84">
-        <v>-1844.214976175511</v>
+        <v>-1868.38836687551</v>
       </c>
       <c r="P84">
-        <v>-5532.644928526532</v>
+        <v>-5605.165100626531</v>
       </c>
       <c r="Q84">
-        <v>-4789.044928526531</v>
+        <v>-4861.565100626531</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2941959533059335</v>
+        <v>0.3088074799709885</v>
       </c>
       <c r="T84">
-        <v>4.841699469077401</v>
+        <v>5.126505320199602</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01740513135042187</v>
+        <v>0.01719543097270594</v>
       </c>
       <c r="W84">
-        <v>0.2316958700275705</v>
+        <v>0.231745317376636</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8454,7 +8454,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.06962052540168751</v>
+        <v>0.06878172389082371</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8462,22 +8462,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2448458850176759</v>
+        <v>0.2467458850176759</v>
       </c>
       <c r="C85">
-        <v>-24560.54300761687</v>
+        <v>-25055.8609971464</v>
       </c>
       <c r="D85">
-        <v>9016.33499238313</v>
+        <v>8931.083002853602</v>
       </c>
       <c r="E85">
-        <v>30780.378</v>
+        <v>31190.444</v>
       </c>
       <c r="F85">
-        <v>34035.478</v>
+        <v>34445.544</v>
       </c>
       <c r="G85">
         <v>458.6</v>
@@ -8498,37 +8498,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M85">
-        <v>8025.565712400001</v>
+        <v>8122.259275200001</v>
       </c>
       <c r="N85">
-        <v>-7473.553467502042</v>
+        <v>-7570.247030302042</v>
       </c>
       <c r="O85">
-        <v>-1868.38836687551</v>
+        <v>-1892.56175757551</v>
       </c>
       <c r="P85">
-        <v>-5605.165100626531</v>
+        <v>-5677.685272726531</v>
       </c>
       <c r="Q85">
-        <v>-4861.565100626531</v>
+        <v>-4934.085272726531</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3088074799709885</v>
+        <v>0.3252454474691753</v>
       </c>
       <c r="T85">
-        <v>5.126505320199602</v>
+        <v>5.446911902712078</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01719543097270594</v>
+        <v>0.01699072346112611</v>
       </c>
       <c r="W85">
-        <v>0.231745317376636</v>
+        <v>0.2317935874078665</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.06878172389082371</v>
+        <v>0.06796289384450438</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8544,22 +8544,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2467458850176759</v>
+        <v>0.2486458850176759</v>
       </c>
       <c r="C86">
-        <v>-25055.86099714638</v>
+        <v>-25549.58192415634</v>
       </c>
       <c r="D86">
-        <v>8931.083002853611</v>
+        <v>8847.428075843663</v>
       </c>
       <c r="E86">
-        <v>31190.444</v>
+        <v>31600.51</v>
       </c>
       <c r="F86">
-        <v>34445.54399999999</v>
+        <v>34855.61</v>
       </c>
       <c r="G86">
         <v>458.6</v>
@@ -8580,37 +8580,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M86">
-        <v>8122.259275199999</v>
+        <v>8218.952838000001</v>
       </c>
       <c r="N86">
-        <v>-7570.24703030204</v>
+        <v>-7666.940593102042</v>
       </c>
       <c r="O86">
-        <v>-1892.56175757551</v>
+        <v>-1916.73514827551</v>
       </c>
       <c r="P86">
-        <v>-5677.68527272653</v>
+        <v>-5750.205444826532</v>
       </c>
       <c r="Q86">
-        <v>-4934.08527272653</v>
+        <v>-5006.605444826531</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3252454474691751</v>
+        <v>0.3438751439671202</v>
       </c>
       <c r="T86">
-        <v>5.446911902712074</v>
+        <v>5.81003936289288</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01699072346112612</v>
+        <v>0.01679083259687757</v>
       </c>
       <c r="W86">
-        <v>0.2317935874078665</v>
+        <v>0.2318407216736563</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.06796289384450449</v>
+        <v>0.06716333038751021</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8626,22 +8626,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2486458850176759</v>
+        <v>0.2505458850176758</v>
       </c>
       <c r="C87">
-        <v>-25549.58192415634</v>
+        <v>-26041.7502498888</v>
       </c>
       <c r="D87">
-        <v>8847.428075843663</v>
+        <v>8765.325750111198</v>
       </c>
       <c r="E87">
-        <v>31600.51</v>
+        <v>32010.576</v>
       </c>
       <c r="F87">
-        <v>34855.61</v>
+        <v>35265.676</v>
       </c>
       <c r="G87">
         <v>458.6</v>
@@ -8662,37 +8662,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M87">
-        <v>8218.952838000001</v>
+        <v>8315.6464008</v>
       </c>
       <c r="N87">
-        <v>-7666.940593102042</v>
+        <v>-7763.634155902041</v>
       </c>
       <c r="O87">
-        <v>-1916.73514827551</v>
+        <v>-1940.90853897551</v>
       </c>
       <c r="P87">
-        <v>-5750.205444826532</v>
+        <v>-5822.725616926531</v>
       </c>
       <c r="Q87">
-        <v>-5006.605444826531</v>
+        <v>-5079.125616926531</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3438751439671202</v>
+        <v>0.3651662256790573</v>
       </c>
       <c r="T87">
-        <v>5.81003936289288</v>
+        <v>6.225042174528086</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01679083259687757</v>
+        <v>0.01659559035737899</v>
       </c>
       <c r="W87">
-        <v>0.2318407216736563</v>
+        <v>0.2318867597937301</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.06716333038751021</v>
+        <v>0.06638236142951592</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8708,22 +8708,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2505458850176758</v>
+        <v>0.2524458850176758</v>
       </c>
       <c r="C88">
-        <v>-26041.7502498888</v>
+        <v>-26532.40880039513</v>
       </c>
       <c r="D88">
-        <v>8765.325750111198</v>
+        <v>8684.733199604872</v>
       </c>
       <c r="E88">
-        <v>32010.576</v>
+        <v>32420.642</v>
       </c>
       <c r="F88">
-        <v>35265.676</v>
+        <v>35675.742</v>
       </c>
       <c r="G88">
         <v>458.6</v>
@@ -8744,37 +8744,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M88">
-        <v>8315.6464008</v>
+        <v>8412.339963599999</v>
       </c>
       <c r="N88">
-        <v>-7763.634155902041</v>
+        <v>-7860.32771870204</v>
       </c>
       <c r="O88">
-        <v>-1940.90853897551</v>
+        <v>-1965.08192967551</v>
       </c>
       <c r="P88">
-        <v>-5822.725616926531</v>
+        <v>-5895.24578902653</v>
       </c>
       <c r="Q88">
-        <v>-5079.125616926531</v>
+        <v>-5151.64578902653</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3651662256790573</v>
+        <v>0.3897328584236002</v>
       </c>
       <c r="T88">
-        <v>6.225042174528086</v>
+        <v>6.703891572568708</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01659559035737899</v>
+        <v>0.01640483644522521</v>
       </c>
       <c r="W88">
-        <v>0.2318867597937301</v>
+        <v>0.2319317395662159</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.06638236142951592</v>
+        <v>0.06561934578090078</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8790,22 +8790,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2524458850176758</v>
+        <v>0.2543458850176759</v>
       </c>
       <c r="C89">
-        <v>-26532.40880039513</v>
+        <v>-27021.5988410246</v>
       </c>
       <c r="D89">
-        <v>8684.733199604872</v>
+        <v>8605.609158975396</v>
       </c>
       <c r="E89">
-        <v>32420.642</v>
+        <v>32830.708</v>
       </c>
       <c r="F89">
-        <v>35675.742</v>
+        <v>36085.808</v>
       </c>
       <c r="G89">
         <v>458.6</v>
@@ -8826,37 +8826,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M89">
-        <v>8412.339963599999</v>
+        <v>8509.0335264</v>
       </c>
       <c r="N89">
-        <v>-7860.32771870204</v>
+        <v>-7957.021281502041</v>
       </c>
       <c r="O89">
-        <v>-1965.08192967551</v>
+        <v>-1989.25532037551</v>
       </c>
       <c r="P89">
-        <v>-5895.24578902653</v>
+        <v>-5967.765961126531</v>
       </c>
       <c r="Q89">
-        <v>-5151.64578902653</v>
+        <v>-5224.16596112653</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3897328584236002</v>
+        <v>0.4183939299589002</v>
       </c>
       <c r="T89">
-        <v>6.703891572568708</v>
+        <v>7.262549203616101</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01640483644522521</v>
+        <v>0.01621841784925674</v>
       </c>
       <c r="W89">
-        <v>0.2319317395662159</v>
+        <v>0.2319756970711453</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.06561934578090078</v>
+        <v>0.06487367139702693</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8872,22 +8872,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2543458850176759</v>
+        <v>0.2562458850176759</v>
       </c>
       <c r="C90">
-        <v>-27021.5988410246</v>
+        <v>-27509.36014687808</v>
       </c>
       <c r="D90">
-        <v>8605.609158975396</v>
+        <v>8527.91385312192</v>
       </c>
       <c r="E90">
-        <v>32830.708</v>
+        <v>33240.774</v>
       </c>
       <c r="F90">
-        <v>36085.808</v>
+        <v>36495.874</v>
       </c>
       <c r="G90">
         <v>458.6</v>
@@ -8908,37 +8908,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M90">
-        <v>8509.0335264</v>
+        <v>8605.7270892</v>
       </c>
       <c r="N90">
-        <v>-7957.021281502041</v>
+        <v>-8053.714844302041</v>
       </c>
       <c r="O90">
-        <v>-1989.25532037551</v>
+        <v>-2013.42871107551</v>
       </c>
       <c r="P90">
-        <v>-5967.765961126531</v>
+        <v>-6040.28613322653</v>
       </c>
       <c r="Q90">
-        <v>-5224.16596112653</v>
+        <v>-5296.68613322653</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4183939299589002</v>
+        <v>0.4522661054097094</v>
       </c>
       <c r="T90">
-        <v>7.262549203616101</v>
+        <v>7.922780949399383</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01621841784925674</v>
+        <v>0.01603618843522015</v>
       </c>
       <c r="W90">
-        <v>0.2319756970711453</v>
+        <v>0.2320186667669751</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.06487367139702693</v>
+        <v>0.06414475374088058</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8954,22 +8954,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2562458850176759</v>
+        <v>0.2581458850176759</v>
       </c>
       <c r="C91">
-        <v>-27509.36014687808</v>
+        <v>-27995.73106947917</v>
       </c>
       <c r="D91">
-        <v>8527.91385312192</v>
+        <v>8451.608930520837</v>
       </c>
       <c r="E91">
-        <v>33240.774</v>
+        <v>33650.84</v>
       </c>
       <c r="F91">
-        <v>36495.874</v>
+        <v>36905.94</v>
       </c>
       <c r="G91">
         <v>458.6</v>
@@ -8990,37 +8990,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M91">
-        <v>8605.7270892</v>
+        <v>8702.420652000001</v>
       </c>
       <c r="N91">
-        <v>-8053.714844302041</v>
+        <v>-8150.408407102042</v>
       </c>
       <c r="O91">
-        <v>-2013.42871107551</v>
+        <v>-2037.60210177551</v>
       </c>
       <c r="P91">
-        <v>-6040.28613322653</v>
+        <v>-6112.806305326531</v>
       </c>
       <c r="Q91">
-        <v>-5296.68613322653</v>
+        <v>-5369.206305326531</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4522661054097094</v>
+        <v>0.4929127159506803</v>
       </c>
       <c r="T91">
-        <v>7.922780949399383</v>
+        <v>8.715059044339322</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01603618843522015</v>
+        <v>0.0158580085637177</v>
       </c>
       <c r="W91">
-        <v>0.2320186667669751</v>
+        <v>0.2320606815806754</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.06414475374088058</v>
+        <v>0.06343203425487076</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9036,22 +9036,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2581458850176759</v>
+        <v>0.2600458850176758</v>
       </c>
       <c r="C92">
-        <v>-27995.73106947917</v>
+        <v>-28480.74859989789</v>
       </c>
       <c r="D92">
-        <v>8451.608930520837</v>
+        <v>8376.657400102113</v>
       </c>
       <c r="E92">
-        <v>33650.84</v>
+        <v>34060.906</v>
       </c>
       <c r="F92">
-        <v>36905.94</v>
+        <v>37316.006</v>
       </c>
       <c r="G92">
         <v>458.6</v>
@@ -9072,37 +9072,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M92">
-        <v>8702.420652000001</v>
+        <v>8799.1142148</v>
       </c>
       <c r="N92">
-        <v>-8150.408407102042</v>
+        <v>-8247.10196990204</v>
       </c>
       <c r="O92">
-        <v>-2037.60210177551</v>
+        <v>-2061.77549247551</v>
       </c>
       <c r="P92">
-        <v>-6112.806305326531</v>
+        <v>-6185.32647742653</v>
       </c>
       <c r="Q92">
-        <v>-5369.206305326531</v>
+        <v>-5441.72647742653</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4929127159506803</v>
+        <v>0.542591906611867</v>
       </c>
       <c r="T92">
-        <v>8.715059044339322</v>
+        <v>9.683398938154802</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0158580085637177</v>
+        <v>0.01568374473334718</v>
       </c>
       <c r="W92">
-        <v>0.2320606815806754</v>
+        <v>0.2321017729918767</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.06343203425487076</v>
+        <v>0.06273497893338886</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9118,22 +9118,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2600458850176758</v>
+        <v>0.2619458850176759</v>
       </c>
       <c r="C93">
-        <v>-28480.74859989789</v>
+        <v>-28964.44842854511</v>
       </c>
       <c r="D93">
-        <v>8376.657400102113</v>
+        <v>8303.023571454891</v>
       </c>
       <c r="E93">
-        <v>34060.906</v>
+        <v>34470.972</v>
       </c>
       <c r="F93">
-        <v>37316.006</v>
+        <v>37726.072</v>
       </c>
       <c r="G93">
         <v>458.6</v>
@@ -9154,37 +9154,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M93">
-        <v>8799.1142148</v>
+        <v>8895.807777600001</v>
       </c>
       <c r="N93">
-        <v>-8247.10196990204</v>
+        <v>-8343.795532702041</v>
       </c>
       <c r="O93">
-        <v>-2061.77549247551</v>
+        <v>-2085.94888317551</v>
       </c>
       <c r="P93">
-        <v>-6185.32647742653</v>
+        <v>-6257.846649526531</v>
       </c>
       <c r="Q93">
-        <v>-5441.72647742653</v>
+        <v>-5514.246649526531</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.542591906611867</v>
+        <v>0.6046908949383505</v>
       </c>
       <c r="T93">
-        <v>9.683398938154802</v>
+        <v>10.89382380542416</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01568374473334718</v>
+        <v>0.01551326924711514</v>
       </c>
       <c r="W93">
-        <v>0.2321017729918767</v>
+        <v>0.2321419711115303</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.06273497893338886</v>
+        <v>0.06205307698846063</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9200,22 +9200,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2619458850176759</v>
+        <v>0.2638458850176759</v>
       </c>
       <c r="C94">
-        <v>-28964.44842854511</v>
+        <v>-29446.86500184066</v>
       </c>
       <c r="D94">
-        <v>8303.023571454891</v>
+        <v>8230.67299815934</v>
       </c>
       <c r="E94">
-        <v>34470.972</v>
+        <v>34881.038</v>
       </c>
       <c r="F94">
-        <v>37726.072</v>
+        <v>38136.138</v>
       </c>
       <c r="G94">
         <v>458.6</v>
@@ -9236,37 +9236,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M94">
-        <v>8895.807777600001</v>
+        <v>8992.5013404</v>
       </c>
       <c r="N94">
-        <v>-8343.795532702041</v>
+        <v>-8440.48909550204</v>
       </c>
       <c r="O94">
-        <v>-2085.94888317551</v>
+        <v>-2110.12227387551</v>
       </c>
       <c r="P94">
-        <v>-6257.846649526531</v>
+        <v>-6330.366821626531</v>
       </c>
       <c r="Q94">
-        <v>-5514.246649526531</v>
+        <v>-5586.76682162653</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6046908949383505</v>
+        <v>0.6845324513581149</v>
       </c>
       <c r="T94">
-        <v>10.89382380542416</v>
+        <v>12.45008434905618</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01551326924711514</v>
+        <v>0.01534645990037197</v>
       </c>
       <c r="W94">
-        <v>0.2321419711115303</v>
+        <v>0.2321813047554923</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.06205307698846063</v>
+        <v>0.06138583960148802</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9282,22 +9282,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2638458850176759</v>
+        <v>0.2657458850176759</v>
       </c>
       <c r="C95">
-        <v>-29446.86500184066</v>
+        <v>-29928.03157594436</v>
       </c>
       <c r="D95">
-        <v>8230.67299815934</v>
+        <v>8159.57242405564</v>
       </c>
       <c r="E95">
-        <v>34881.038</v>
+        <v>35291.104</v>
       </c>
       <c r="F95">
-        <v>38136.138</v>
+        <v>38546.204</v>
       </c>
       <c r="G95">
         <v>458.6</v>
@@ -9318,37 +9318,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M95">
-        <v>8992.5013404</v>
+        <v>9089.194903199999</v>
       </c>
       <c r="N95">
-        <v>-8440.48909550204</v>
+        <v>-8537.182658302039</v>
       </c>
       <c r="O95">
-        <v>-2110.12227387551</v>
+        <v>-2134.29566457551</v>
       </c>
       <c r="P95">
-        <v>-6330.366821626531</v>
+        <v>-6402.88699372653</v>
       </c>
       <c r="Q95">
-        <v>-5586.76682162653</v>
+        <v>-5659.28699372653</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6845324513581149</v>
+        <v>0.790987859917801</v>
       </c>
       <c r="T95">
-        <v>12.45008434905618</v>
+        <v>14.52509840723221</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01534645990037197</v>
+        <v>0.01518319968866589</v>
       </c>
       <c r="W95">
-        <v>0.2321813047554923</v>
+        <v>0.2322198015134126</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.06138583960148802</v>
+        <v>0.06073279875466364</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9364,22 +9364,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2657458850176759</v>
+        <v>0.2676458850176759</v>
       </c>
       <c r="C96">
-        <v>-29928.03157594436</v>
+        <v>-30407.98026772596</v>
       </c>
       <c r="D96">
-        <v>8159.57242405564</v>
+        <v>8089.689732274045</v>
       </c>
       <c r="E96">
-        <v>35291.104</v>
+        <v>35701.17000000001</v>
       </c>
       <c r="F96">
-        <v>38546.204</v>
+        <v>38956.27</v>
       </c>
       <c r="G96">
         <v>458.6</v>
@@ -9400,37 +9400,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M96">
-        <v>9089.194903199999</v>
+        <v>9185.888466000002</v>
       </c>
       <c r="N96">
-        <v>-8537.182658302039</v>
+        <v>-8633.876221102042</v>
       </c>
       <c r="O96">
-        <v>-2134.29566457551</v>
+        <v>-2158.469055275511</v>
       </c>
       <c r="P96">
-        <v>-6402.88699372653</v>
+        <v>-6475.407165826531</v>
       </c>
       <c r="Q96">
-        <v>-5659.28699372653</v>
+        <v>-5731.807165826531</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.790987859917801</v>
+        <v>0.9400254319013616</v>
       </c>
       <c r="T96">
-        <v>14.52509840723221</v>
+        <v>17.43011808867866</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01518319968866589</v>
+        <v>0.01502337653404835</v>
       </c>
       <c r="W96">
-        <v>0.2322198015134126</v>
+        <v>0.2322574878132714</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.06073279875466364</v>
+        <v>0.06009350613619346</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9446,22 +9446,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2676458850176759</v>
+        <v>0.2695458850176758</v>
       </c>
       <c r="C97">
-        <v>-30407.98026772596</v>
+        <v>-30886.74210313811</v>
       </c>
       <c r="D97">
-        <v>8089.689732274045</v>
+        <v>8020.993896861894</v>
       </c>
       <c r="E97">
-        <v>35701.17000000001</v>
+        <v>36111.236</v>
       </c>
       <c r="F97">
-        <v>38956.27</v>
+        <v>39366.336</v>
       </c>
       <c r="G97">
         <v>458.6</v>
@@ -9482,37 +9482,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M97">
-        <v>9185.888466000002</v>
+        <v>9282.582028800001</v>
       </c>
       <c r="N97">
-        <v>-8633.876221102042</v>
+        <v>-8730.569783902041</v>
       </c>
       <c r="O97">
-        <v>-2158.469055275511</v>
+        <v>-2182.64244597551</v>
       </c>
       <c r="P97">
-        <v>-6475.407165826531</v>
+        <v>-6547.927337926531</v>
       </c>
       <c r="Q97">
-        <v>-5731.807165826531</v>
+        <v>-5804.32733792653</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9400254319013616</v>
+        <v>1.163581789876702</v>
       </c>
       <c r="T97">
-        <v>17.43011808867866</v>
+        <v>21.78764761084834</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01502337653404835</v>
+        <v>0.01486688302848535</v>
       </c>
       <c r="W97">
-        <v>0.2322574878132714</v>
+        <v>0.2322943889818831</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.06009350613619346</v>
+        <v>0.05946753211394151</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9528,22 +9528,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2695458850176758</v>
+        <v>0.2714458850176759</v>
       </c>
       <c r="C98">
-        <v>-30886.7421031381</v>
+        <v>-31364.34706314548</v>
       </c>
       <c r="D98">
-        <v>8020.993896861894</v>
+        <v>7953.454936854518</v>
       </c>
       <c r="E98">
-        <v>36111.236</v>
+        <v>36521.302</v>
       </c>
       <c r="F98">
-        <v>39366.336</v>
+        <v>39776.40199999999</v>
       </c>
       <c r="G98">
         <v>458.6</v>
@@ -9564,37 +9564,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M98">
-        <v>9282.5820288</v>
+        <v>9379.275591599999</v>
       </c>
       <c r="N98">
-        <v>-8730.569783902039</v>
+        <v>-8827.263346702039</v>
       </c>
       <c r="O98">
-        <v>-2182.64244597551</v>
+        <v>-2206.81583667551</v>
       </c>
       <c r="P98">
-        <v>-6547.92733792653</v>
+        <v>-6620.447510026529</v>
       </c>
       <c r="Q98">
-        <v>-5804.327337926529</v>
+        <v>-5876.847510026529</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.1635817898767</v>
+        <v>1.5361757198356</v>
       </c>
       <c r="T98">
-        <v>21.78764761084828</v>
+        <v>29.05019681446438</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01486688302848535</v>
+        <v>0.01471361619314014</v>
       </c>
       <c r="W98">
-        <v>0.2322943889818831</v>
+        <v>0.2323305293016576</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.05946753211394151</v>
+        <v>0.05885446477256062</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9610,22 +9610,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2714458850176759</v>
+        <v>0.2733458850176759</v>
       </c>
       <c r="C99">
-        <v>-31364.34706314548</v>
+        <v>-31840.82412735282</v>
       </c>
       <c r="D99">
-        <v>7953.454936854518</v>
+        <v>7887.043872647182</v>
       </c>
       <c r="E99">
-        <v>36521.302</v>
+        <v>36931.368</v>
       </c>
       <c r="F99">
-        <v>39776.40199999999</v>
+        <v>40186.468</v>
       </c>
       <c r="G99">
         <v>458.6</v>
@@ -9646,37 +9646,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M99">
-        <v>9379.275591599999</v>
+        <v>9475.9691544</v>
       </c>
       <c r="N99">
-        <v>-8827.263346702039</v>
+        <v>-8923.95690950204</v>
       </c>
       <c r="O99">
-        <v>-2206.81583667551</v>
+        <v>-2230.98922737551</v>
       </c>
       <c r="P99">
-        <v>-6620.447510026529</v>
+        <v>-6692.967682126529</v>
       </c>
       <c r="Q99">
-        <v>-5876.847510026529</v>
+        <v>-5949.367682126529</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.5361757198356</v>
+        <v>2.281363579753399</v>
       </c>
       <c r="T99">
-        <v>29.05019681446438</v>
+        <v>43.57529522169656</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01471361619314014</v>
+        <v>0.01456347725239381</v>
       </c>
       <c r="W99">
-        <v>0.2323305293016576</v>
+        <v>0.2323659320638855</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.05885446477256062</v>
+        <v>0.05825390900957528</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9692,22 +9692,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2733458850176759</v>
+        <v>0.2752458850176758</v>
       </c>
       <c r="C100">
-        <v>-31840.82412735282</v>
+        <v>-32316.20131546532</v>
       </c>
       <c r="D100">
-        <v>7887.043872647182</v>
+        <v>7821.732684534681</v>
       </c>
       <c r="E100">
-        <v>36931.368</v>
+        <v>37341.434</v>
       </c>
       <c r="F100">
-        <v>40186.468</v>
+        <v>40596.534</v>
       </c>
       <c r="G100">
         <v>458.6</v>
@@ -9728,37 +9728,37 @@
         <v>552.0122448979592</v>
       </c>
       <c r="M100">
-        <v>9475.9691544</v>
+        <v>9572.662717200001</v>
       </c>
       <c r="N100">
-        <v>-8923.95690950204</v>
+        <v>-9020.650472302041</v>
       </c>
       <c r="O100">
-        <v>-2230.98922737551</v>
+        <v>-2255.16261807551</v>
       </c>
       <c r="P100">
-        <v>-6692.967682126529</v>
+        <v>-6765.487854226531</v>
       </c>
       <c r="Q100">
-        <v>-5949.367682126529</v>
+        <v>-6021.88785422653</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.281363579753399</v>
+        <v>4.516927159506798</v>
       </c>
       <c r="T100">
-        <v>43.57529522169656</v>
+        <v>87.15059044339313</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01456347725239381</v>
+        <v>0.01441637142156155</v>
       </c>
       <c r="W100">
-        <v>0.2323659320638855</v>
+        <v>0.2324006196187958</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9766,91 +9766,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.05825390900957528</v>
+        <v>0.0576654856862463</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2752458850176758</v>
-      </c>
-      <c r="C101">
-        <v>-32316.20131546532</v>
-      </c>
-      <c r="D101">
-        <v>7821.732684534681</v>
-      </c>
-      <c r="E101">
-        <v>37341.434</v>
-      </c>
-      <c r="F101">
-        <v>40596.534</v>
-      </c>
-      <c r="G101">
-        <v>458.6</v>
-      </c>
-      <c r="H101">
-        <v>37751.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1295.612244897959</v>
-      </c>
-      <c r="K101">
-        <v>743.6</v>
-      </c>
-      <c r="L101">
-        <v>552.0122448979592</v>
-      </c>
-      <c r="M101">
-        <v>9572.662717200001</v>
-      </c>
-      <c r="N101">
-        <v>-9020.650472302041</v>
-      </c>
-      <c r="O101">
-        <v>-2255.16261807551</v>
-      </c>
-      <c r="P101">
-        <v>-6765.487854226531</v>
-      </c>
-      <c r="Q101">
-        <v>-6021.88785422653</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.516927159506798</v>
-      </c>
-      <c r="T101">
-        <v>87.15059044339313</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01441637142156155</v>
-      </c>
-      <c r="W101">
-        <v>0.2324006196187958</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.0576654856862463</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
